--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,21 +117,24 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -218,7 +226,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Estado de los 98 casos</a:t>
+              <a:t>Estado de los 190 casos</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -238,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Reporte de ejecución - Entrega2'!$A$105:$A$108</f>
+              <f>'Reporte de ejecución - Entrega2'!$A$197:$A$201</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Reporte de ejecución - Entrega2'!$B$105:$B$108</f>
+              <f>'Reporte de ejecución - Entrega2'!$B$197:$B$201</f>
             </numRef>
           </val>
         </ser>
@@ -596,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +619,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biyu - entrega 2 - Reporte de ejecución de test cases (Deudas 018–029 y Navegación)</t>
+          <t>Biyu - entrega 2 - Reporte de ejecución de test cases (Deudas 018–029 y 100–159, y Navegación)</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1092,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-001</t>
+          <t>CP-DEU-100</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1094,17 +1102,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>La barra tiene cuatro secciones en el orden correcto</t>
+          <t>Abrir la dirección de «Saldadas» y recargar mantiene el filtro</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1117,27 +1125,27 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-002</t>
+          <t>CP-DEU-101</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>«Registrar» lleva a Registrar</t>
+          <t>Un filtro inválido en la dirección se trata como «Pendientes»</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1150,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-003</t>
+          <t>CP-DEU-102</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1160,17 +1168,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>«Resumen» lleva al Resumen</t>
+          <t>Deudas pendientes: la de fecha más nueva va primero</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1183,7 +1191,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-004</t>
+          <t>CP-DEU-102B</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1193,17 +1201,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>«Deudas» lleva a Deudas</t>
+          <t>Deudas saldadas: la saldada más recientemente va primero</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1216,7 +1224,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-005</t>
+          <t>CP-DEU-103</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1226,17 +1234,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>«Suscripciones» lleva a Suscripciones</t>
+          <t>Sin deudas pendientes: mensaje y botón «Cargar una deuda»</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1249,27 +1257,27 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-006</t>
+          <t>CP-DEU-104</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>En Registrar la barra marca «Registrar»</t>
+          <t>Sin deudas saldadas: mensaje y sin botón</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1282,27 +1290,27 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-007</t>
+          <t>CP-DEU-105</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>En el Resumen la barra marca «Resumen»</t>
+          <t>Sin ninguna deuda en «Todas»: mensaje y botón «Cargar una deuda»</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1315,27 +1323,27 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-008</t>
+          <t>CP-DEU-106</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>En Movimientos la barra sigue marcando «Resumen»</t>
+          <t>Otro usuario no ve las deudas de alguien más</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1348,27 +1356,27 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-009</t>
+          <t>CP-DEU-107</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>En Movimientos eliminados la barra sigue marcando «Resumen»</t>
+          <t>Por API, otro usuario no recibe las deudas de alguien más</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1381,27 +1389,27 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-010</t>
+          <t>CP-DEU-108</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>En Deudas la barra marca «Deudas»</t>
+          <t>Por API, sin sesión no se pueden leer las deudas</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1414,27 +1422,27 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-011</t>
+          <t>CP-DEU-108B</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>En Suscripciones la barra marca «Suscripciones»</t>
+          <t>Sin sesión, la dirección /debts lleva al login</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1447,27 +1455,27 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-012</t>
+          <t>CP-DEU-108C</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>En Ajustes no se marca ninguna de las cuatro secciones</t>
+          <t>Sin sesión, la dirección /debts/new lleva al login</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-36, US-38</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1480,27 +1488,27 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-013</t>
+          <t>CP-DEU-109</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Pantalla muy angosta (320 px): los nombres se leen completos</t>
+          <t>Marcar una deuda como saldada desde «Pendientes»</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30, US-37, US-39</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1513,27 +1521,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-014</t>
+          <t>CP-DEU-110</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Pantalla angosta (320 px): los botones son cómodos de tocar</t>
+          <t>Marcar saldada desde «Todas» deja la fila como saldada</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1546,22 +1554,22 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-015</t>
+          <t>CP-DEU-111</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Ancho 1023 px: barra abajo y engranaje de Ajustes</t>
+          <t>«Deshacer» devuelve la deuda a pendiente</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1579,7 +1587,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-016</t>
+          <t>CP-DEU-111B</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1589,12 +1597,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Ancho 1024 px: barra lateral con Ajustes al pie</t>
+          <t>El aviso con «Deshacer» desaparece al cambiar de filtro</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1612,7 +1620,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-017</t>
+          <t>CP-DEU-112</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1622,12 +1630,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Ancho 1280 px: se mantiene la barra lateral</t>
+          <t>Saldar una deuda que ya se saldó en otra pestaña muestra un error</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1645,27 +1653,27 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-018</t>
+          <t>CP-DEU-113</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Registrar (375 px)</t>
+          <t>Por API, saldar una deuda ya saldada se rechaza</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1678,27 +1686,27 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-019</t>
+          <t>CP-DEU-114</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Registrar (1023 px)</t>
+          <t>Por API, un usuario no puede saldar la deuda de otro</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1711,7 +1719,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-020</t>
+          <t>CP-DEU-114B</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1721,12 +1729,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Registrar (1024 px)</t>
+          <t>Por API, saldar una deuda que no existe se rechaza</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1744,22 +1752,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-021</t>
+          <t>CP-DEU-115</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Registrar (1280 px)</t>
+          <t>Por API, sin sesión no se puede saldar una deuda</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1777,27 +1785,27 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-022</t>
+          <t>CP-DEU-116</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>«Ver todos» y «‹ Resumen» mantienen el mes</t>
+          <t>Por API, no se puede modificar una deuda directamente</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1810,27 +1818,27 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-023</t>
+          <t>CP-DEU-116B</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Con el mes vacío se llega igual a los movimientos eliminados</t>
+          <t>Por API, no se puede borrar una deuda directamente</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1843,22 +1851,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-024</t>
+          <t>CP-DEU-117</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Deudas no arrastra el mes del Resumen</t>
+          <t>«Volver a pendiente» desde «Saldadas»</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1876,22 +1884,22 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-025</t>
+          <t>CP-DEU-118</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Suscripciones no arrastra el mes del Resumen</t>
+          <t>«Volver a pendiente» desde «Todas» actualiza los totales</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-37, US-40</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1909,27 +1917,27 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-026</t>
+          <t>CP-DEU-119</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Del Movimiento al Resumen se conserva el mes</t>
+          <t>Por API, reabrir una deuda que ya está pendiente se rechaza</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1942,27 +1950,27 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-027</t>
+          <t>CP-DEU-119B</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Tocar «Registrar» estando en Registrar no pierde lo cargado</t>
+          <t>Volver a pendiente una deuda que ya se reabrió en otra pestaña muestra un error</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -1975,27 +1983,27 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-028</t>
+          <t>CP-DEU-120</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Escribir /transactions abre Movimientos con la barra nueva</t>
+          <t>Por API, un usuario no puede reabrir la deuda de otro</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2008,7 +2016,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-029</t>
+          <t>CP-DEU-120B</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2018,17 +2026,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>El aviso al borrar explica cómo restaurar un gasto</t>
+          <t>Por API, reabrir una deuda que no existe se rechaza</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>US-65, US-69</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2041,27 +2049,27 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-030</t>
+          <t>CP-DEU-121</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Guardar $12.500 muestra la confirmación completa</t>
+          <t>Por API, sin sesión no se puede reabrir una deuda</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>US-10, US-70</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2074,7 +2082,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-031</t>
+          <t>CP-DEU-122</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2084,17 +2092,17 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Guardar $120.000 en 12 cuotas lo dice en el aviso</t>
+          <t>Saldar y reabrir tres veces seguidas deja la deuda pendiente</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>US-10, US-70</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2107,7 +2115,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-032</t>
+          <t>CP-DEU-123</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2117,17 +2125,17 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Sin internet el gasto no se pierde y aparece «Reintentar»</t>
+          <t>Filtro por dirección: «Todas», «Te deben» y «Debés»</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2140,27 +2148,27 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-033</t>
+          <t>CP-DEU-124</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>El aviso de error no desaparece solo</t>
+          <t>Los filtros de estado y de dirección se combinan</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2173,27 +2181,27 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-034</t>
+          <t>CP-DEU-125</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Reintentar al volver internet guarda una sola vez</t>
+          <t>Una dirección inválida se trata como «Todas»</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2206,27 +2214,27 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-035</t>
+          <t>CP-DEU-126</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Cambiar el monto después del fallo empieza un intento nuevo</t>
+          <t>Sin deudas: «Pendientes» + «Te deben»</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2239,27 +2247,27 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-036</t>
+          <t>CP-DEU-126B</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Guardar el gasto corregido elimina el pendiente anterior</t>
+          <t>Sin deudas: «Saldadas» + «Te deben»</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2272,22 +2280,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-037</t>
+          <t>CP-DEU-126C</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Dos fallos seguidos dejan un solo pendiente</t>
+          <t>Sin deudas: «Todas» + «Te deben»</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2305,22 +2313,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-038</t>
+          <t>CP-DEU-127</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Con internet muy lenta, a los 15 segundos avisa que falló</t>
+          <t>Sin deudas: «Pendientes» + «Debés»</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2338,27 +2346,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-039</t>
+          <t>CP-DEU-127B</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Reintentar no duplica un gasto que ya se había guardado</t>
+          <t>Sin deudas: «Saldadas» + «Debés»</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2371,27 +2379,27 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-040</t>
+          <t>CP-DEU-127C</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>La misma clave dos veces seguidas devuelve el mismo gasto</t>
+          <t>Sin deudas: «Todas» + «Debés»</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2404,7 +2412,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-041</t>
+          <t>CP-DEU-128</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2414,12 +2422,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Dos pedidos simultáneos con la misma clave crean un solo gasto</t>
+          <t>Gasto compartido con varias personas: agregar, quitar y guardar</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2427,9 +2435,9 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G56" s="3" t="n"/>
@@ -2437,32 +2445,32 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-042</t>
+          <t>CP-DEU-128B</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Claves distintas con el mismo contenido crean dos gastos</t>
+          <t>Las personas se ordenan por nombre sin distinguir mayúsculas ni tildes</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-38, US-82</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G57" s="3" t="n"/>
@@ -2470,7 +2478,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-043</t>
+          <t>CP-DEU-129</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2480,12 +2488,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>La misma clave en dos usuarios distintos no se pisa</t>
+          <t>«Dividir en partes iguales» entre 2 personas</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2493,9 +2501,9 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
@@ -2503,32 +2511,32 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-044</t>
+          <t>CP-DEU-129B</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>La misma clave con otro monto conserva el gasto original</t>
+          <t>Dividir un gasto de $0,02 entre 2 personas da error</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G59" s="3" t="n"/>
@@ -2536,32 +2544,32 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-045</t>
+          <t>CP-DEU-129C</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>La misma clave sigue funcionando después de archivar la categoría</t>
+          <t>«Dividir en partes iguales» con los nombres vacíos</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G60" s="3" t="n"/>
@@ -2569,32 +2577,32 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-046</t>
+          <t>CP-DEU-130</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Sin clave, cada llamada crea un gasto distinto</t>
+          <t>«Dividir en partes iguales» entre 3 personas</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G61" s="3" t="n"/>
@@ -2602,22 +2610,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-047</t>
+          <t>CP-DEU-130B</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Si se archiva la categoría antes de guardar, el gasto se rechaza con aviso</t>
+          <t>Cambiar la moneda con personas cargadas vacía los montos</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2625,9 +2633,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G62" s="3" t="n"/>
@@ -2635,22 +2643,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-048</t>
+          <t>CP-DEU-130C</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>La API rechaza un gasto con una categoría archivada</t>
+          <t>«Dividir en partes iguales» en dólares</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2658,9 +2666,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G63" s="3" t="n"/>
@@ -2668,32 +2676,32 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-049</t>
+          <t>CP-DEU-130D</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Al volver a Registrar aparece el gasto pendiente</t>
+          <t>En dólares, dividir un gasto muy chico da error de centavos</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-34, US-82</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G64" s="3" t="n"/>
@@ -2701,7 +2709,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-050</t>
+          <t>CP-DEU-131</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2711,22 +2719,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Al recargar la página sigue el gasto pendiente</t>
+          <t>Entre todos pueden deber todo el gasto (tu parte es $0)</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G65" s="3" t="n"/>
@@ -2734,7 +2742,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-051</t>
+          <t>CP-DEU-132</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2744,22 +2752,22 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Dos gastos fallidos: dos pendientes, el más nuevo primero</t>
+          <t>La suma de lo que te deben no puede superar el gasto</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G66" s="3" t="n"/>
@@ -2767,32 +2775,32 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-052</t>
+          <t>CP-DEU-132B</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Recuperar un gasto en dólares conserva fecha y tipo de cambio</t>
+          <t>Bajar el gasto por debajo de lo que te deben da error</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G67" s="3" t="n"/>
@@ -2800,32 +2808,32 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-053</t>
+          <t>CP-DEU-132C</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Recuperar un gasto que en realidad ya estaba guardado</t>
+          <t>Una persona que debe más que el gasto da error en su fila</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-41, US-82</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G68" s="3" t="n"/>
@@ -2833,32 +2841,32 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-054</t>
+          <t>CP-DEU-132D</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Recuperar un gasto que ya estaba guardado y fue eliminado</t>
+          <t>Bajar el gasto muy por debajo da error en cada fila</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G69" s="3" t="n"/>
@@ -2866,7 +2874,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-055</t>
+          <t>CP-DEU-133</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2876,12 +2884,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Recuperar sin internet no pierde el pendiente</t>
+          <t>Se puede compartir con hasta 10 personas</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2889,9 +2897,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G70" s="3" t="n"/>
@@ -2899,7 +2907,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-056</t>
+          <t>CP-DEU-134</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2909,22 +2917,22 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Descartar borra el pendiente, incluso al recargar</t>
+          <t>No se puede repetir una persona</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G71" s="3" t="n"/>
@@ -2932,32 +2940,32 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-057</t>
+          <t>CP-DEU-135</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión borra los pendientes</t>
+          <t>Una persona sin nombre da error en su fila</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G72" s="3" t="n"/>
@@ -2965,32 +2973,32 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-058</t>
+          <t>CP-DEU-135B</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Recuperar con la categoría archivada deja la categoría vacía</t>
+          <t>Quitar una persona conserva a las demás</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>US-11, US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G73" s="3" t="n"/>
@@ -2998,32 +3006,32 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-059</t>
+          <t>CP-DEU-135C</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Un pendiente de septiembre se guarda en septiembre</t>
+          <t>Pasar a Ingreso y volver a Gasto reinicia la sección compartida</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G74" s="3" t="n"/>
@@ -3031,7 +3039,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-060</t>
+          <t>CP-DEU-135D</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3041,22 +3049,22 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Un lector de pantalla (TalkBack) anuncia el error sin mover el foco</t>
+          <t>Apagar «Gasto compartido» guarda el gasto sin deudas</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>NO EJECUTADO</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G75" s="3" t="n"/>
@@ -3064,7 +3072,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-061</t>
+          <t>CP-DEU-136</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3074,22 +3082,22 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Tocar dos veces «Guardar» guarda una sola vez</t>
+          <t>Gasto compartido con 3 personas en 2 cuotas: etiqueta en Movimientos y Resumen</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G76" s="3" t="n"/>
@@ -3097,22 +3105,22 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-062</t>
+          <t>CP-DEU-136B</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>El primer gasto guiado también conserva los datos y ofrece «Reintentar»</t>
+          <t>Al borrar un gasto con varias deudas, el aviso las lista</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>US-68, US-70</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -3120,9 +3128,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G77" s="3" t="n"/>
@@ -3130,22 +3138,22 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-063</t>
+          <t>CP-DEU-136C</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Resumen (375 px)</t>
+          <t>Las 3 deudas de un mismo gasto aparecen en Deudas</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30, US-37, US-38, US-82</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3153,9 +3161,9 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G78" s="3" t="n"/>
@@ -3163,32 +3171,32 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-064</t>
+          <t>CP-DEU-136D</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Movimientos (375 px)</t>
+          <t>Eliminar el gasto saca sus 3 deudas</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-35, US-82</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G79" s="3" t="n"/>
@@ -3196,32 +3204,32 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-065</t>
+          <t>CP-DEU-136E</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Deudas (375 px)</t>
+          <t>Restaurar el gasto devuelve sus 3 deudas con su estado</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-35, US-82</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G80" s="3" t="n"/>
@@ -3229,32 +3237,32 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-066</t>
+          <t>CP-DEU-137</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Suscripciones (375 px)</t>
+          <t>Por API, 2 personas y 1 monto se rechaza</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G81" s="3" t="n"/>
@@ -3262,7 +3270,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-067</t>
+          <t>CP-DEU-138</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3272,22 +3280,22 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Ajustes (375 px)</t>
+          <t>Por API, listas vacías se rechazan</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G82" s="3" t="n"/>
@@ -3295,32 +3303,32 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-068</t>
+          <t>CP-DEU-139</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Resumen (1023 px)</t>
+          <t>Por API, 11 personas se rechaza</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G83" s="3" t="n"/>
@@ -3328,32 +3336,32 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-069</t>
+          <t>CP-DEU-140</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Movimientos (1023 px)</t>
+          <t>Por API, la misma persona repetida se rechaza</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G84" s="3" t="n"/>
@@ -3361,32 +3369,32 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-070</t>
+          <t>CP-DEU-141</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Deudas (1023 px)</t>
+          <t>Por API, deudas que suman más que el gasto se rechazan</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G85" s="3" t="n"/>
@@ -3394,32 +3402,32 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-071</t>
+          <t>CP-DEU-142</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Suscripciones (1023 px)</t>
+          <t>Dólares: el redondeo hace que las deudas sumen más que el gasto</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G86" s="3" t="n"/>
@@ -3427,32 +3435,32 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-072</t>
+          <t>CP-DEU-142A</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Ajustes (1023 px)</t>
+          <t>Por API, el mismo caso de redondeo se rechaza</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G87" s="3" t="n"/>
@@ -3460,22 +3468,22 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-073</t>
+          <t>CP-DEU-142B</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Resumen (1024 px)</t>
+          <t>Por API, una segunda persona sin nombre se rechaza sin guardar nada</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3483,9 +3491,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G88" s="3" t="n"/>
@@ -3493,27 +3501,27 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-074</t>
+          <t>CP-DEU-143</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Movimientos (1024 px)</t>
+          <t>Resumen: gasto bruto y neto de reembolsos</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3526,27 +3534,27 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-075</t>
+          <t>CP-DEU-144</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Deudas (1024 px)</t>
+          <t>Resumen: el neto no cambia al saldar la deuda</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3559,32 +3567,32 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-076</t>
+          <t>CP-DEU-145</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Suscripciones (1024 px)</t>
+          <t>Resumen: gasto en 12 cuotas con deuda, neto negativo</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>DUDA</t>
         </is>
       </c>
       <c r="G91" s="3" t="n"/>
@@ -3592,22 +3600,22 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-077</t>
+          <t>CP-DEU-146</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Ajustes (1024 px)</t>
+          <t>Resumen: una deuda suelta «Me deben» no cambia el neto</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3625,22 +3633,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-078</t>
+          <t>CP-DEU-147</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Resumen (1280 px)</t>
+          <t>Resumen: una deuda suelta «Debo» no cambia el neto</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -3658,22 +3666,22 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-079</t>
+          <t>CP-DEU-148</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Movimientos (1280 px)</t>
+          <t>Resumen: eliminar un gasto compartido actualiza el neto en vivo</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30, US-35</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3691,22 +3699,22 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-080</t>
+          <t>CP-DEU-148B</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Deudas (1280 px)</t>
+          <t>Resumen: restaurar un gasto compartido vuelve a restar su deuda</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30, US-35</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3724,27 +3732,27 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-081</t>
+          <t>CP-DEU-149</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Suscripciones (1280 px)</t>
+          <t>Resumen: el neto en dólares no cambia si cambia el tipo de cambio</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -3757,7 +3765,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-082</t>
+          <t>CP-DEU-150</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3767,12 +3775,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Ajustes (1280 px)</t>
+          <t>Resumen: sin deudas vinculadas no aparece el neto</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3790,7 +3798,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-083</t>
+          <t>CP-DEU-151</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3800,12 +3808,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>La API devuelve un solo gasto activo para la clave recuperada</t>
+          <t>Balance: una deuda suelta «Me deben» resta del balance del mes</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-83</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3813,9 +3821,9 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G98" s="3" t="n"/>
@@ -3823,7 +3831,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-084</t>
+          <t>CP-DEU-152</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3833,12 +3841,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>La API conserva un solo gasto eliminado para la clave recuperada</t>
+          <t>Balance: una deuda suelta «Debo» suma al balance del mes</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-83</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3846,703 +3854,3946 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>DEF-029</t>
-        </is>
-      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>CP-DEU-153</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Balance: saldar la deuda suelta el mismo mes lo deja como antes</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-153B</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Balance en cero: deuda suelta creada y saldada el mismo mes</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-154</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Balance: una deuda saldada hoy mueve el balance de dos meses</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-155</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Balance: reabrir la deuda saca el evento del mes actual</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-156</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Balance: una deuda suelta «Debo» saldada hoy mueve dos meses</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-157</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Balance: la deuda en dólares conserva el tipo de cambio de origen</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-158</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Balance: un gasto compartido no aparece como deuda suelta</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>DUDA</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>CP-DEU-159</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Un mes solo con una deuda suelta no se ve vacío</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>US-83</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-001</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>La barra tiene cuatro secciones en el orden correcto</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-002</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>«Registrar» lleva a Registrar</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-003</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>«Resumen» lleva al Resumen</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-004</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>«Deudas» lleva a Deudas</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-005</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>«Suscripciones» lleva a Suscripciones</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-006</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>En Registrar la barra marca «Registrar»</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-007</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>En el Resumen la barra marca «Resumen»</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-008</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>En Movimientos la barra sigue marcando «Resumen»</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-009</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>En Movimientos eliminados la barra sigue marcando «Resumen»</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-010</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>En Deudas la barra marca «Deudas»</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-011</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>En Suscripciones la barra marca «Suscripciones»</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-012</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>En Ajustes no se marca ninguna de las cuatro secciones</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-013</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Pantalla muy angosta (320 px): los nombres se leen completos</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-014</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Pantalla angosta (320 px): los botones son cómodos de tocar</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-015</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Ancho 1023 px: barra abajo y engranaje de Ajustes</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-016</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Ancho 1024 px: barra lateral con Ajustes al pie</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-017</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Ancho 1280 px: se mantiene la barra lateral</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-018</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Registrar (375 px)</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-019</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Registrar (1023 px)</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-020</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Registrar (1024 px)</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-021</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Registrar (1280 px)</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-022</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>«Ver todos» y «‹ Resumen» mantienen el mes</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-023</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Con el mes vacío se llega igual a los movimientos eliminados</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-024</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Deudas no arrastra el mes del Resumen</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-025</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Suscripciones no arrastra el mes del Resumen</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-026</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Del Movimiento al Resumen se conserva el mes</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-027</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Tocar «Registrar» estando en Registrar no pierde lo cargado</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-028</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Escribir /transactions abre Movimientos con la barra nueva</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-029</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>El aviso al borrar explica cómo restaurar un gasto</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>US-65, US-69</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-030</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Guardar $12.500 muestra la confirmación completa</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>US-10, US-70</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-031</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Guardar $120.000 en 12 cuotas lo dice en el aviso</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>US-10, US-70</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-032</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Sin internet el gasto no se pierde y aparece «Reintentar»</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-033</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>El aviso de error no desaparece solo</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-034</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Reintentar al volver internet guarda una sola vez</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-035</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Cambiar el monto después del fallo empieza un intento nuevo</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-036</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Guardar el gasto corregido elimina el pendiente anterior</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-037</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Dos fallos seguidos dejan un solo pendiente</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-038</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Con internet muy lenta, a los 15 segundos avisa que falló</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-039</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Reintentar no duplica un gasto que ya se había guardado</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-040</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>La misma clave dos veces seguidas devuelve el mismo gasto</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-041</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Dos pedidos simultáneos con la misma clave crean un solo gasto</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-042</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Claves distintas con el mismo contenido crean dos gastos</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-043</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>La misma clave en dos usuarios distintos no se pisa</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-044</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>La misma clave con otro monto conserva el gasto original</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-045</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>La misma clave sigue funcionando después de archivar la categoría</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-046</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Sin clave, cada llamada crea un gasto distinto</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-047</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Si se archiva la categoría antes de guardar, el gasto se rechaza con aviso</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-048</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>La API rechaza un gasto con una categoría archivada</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-049</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Al volver a Registrar aparece el gasto pendiente</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-050</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Al recargar la página sigue el gasto pendiente</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-051</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Dos gastos fallidos: dos pendientes, el más nuevo primero</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-052</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Recuperar un gasto en dólares conserva fecha y tipo de cambio</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-053</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Recuperar un gasto que en realidad ya estaba guardado</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-054</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Recuperar un gasto que ya estaba guardado y fue eliminado</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-055</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Recuperar sin internet no pierde el pendiente</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-056</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Descartar borra el pendiente, incluso al recargar</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-057</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Cerrar sesión borra los pendientes</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-058</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Recuperar con la categoría archivada deja la categoría vacía</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>US-11, US-70</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-059</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Un pendiente de septiembre se guarda en septiembre</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-060</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Un lector de pantalla (TalkBack) anuncia el error sin mover el foco</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>NO EJECUTADO</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-061</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Tocar dos veces «Guardar» guarda una sola vez</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-062</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>El primer gasto guiado también conserva los datos y ofrece «Reintentar»</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>US-68, US-70</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-063</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Resumen (375 px)</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-064</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Movimientos (375 px)</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-065</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Deudas (375 px)</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-066</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Suscripciones (375 px)</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-067</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Ajustes (375 px)</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-068</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Resumen (1023 px)</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-069</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Movimientos (1023 px)</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-070</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Deudas (1023 px)</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-071</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Suscripciones (1023 px)</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-072</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Ajustes (1023 px)</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-073</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Resumen (1024 px)</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-074</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Movimientos (1024 px)</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-075</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Deudas (1024 px)</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-076</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Suscripciones (1024 px)</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-077</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Ajustes (1024 px)</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-078</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Resumen (1280 px)</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-079</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Movimientos (1280 px)</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-080</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Deudas (1280 px)</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-081</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Suscripciones (1280 px)</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-082</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Identificadores únicos en Ajustes (1280 px)</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>US-69</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-083</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>La API devuelve un solo gasto activo para la clave recuperada</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>CP-NAV-084</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>La API conserva un solo gasto eliminado para la clave recuperada</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>US-70</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>DEF-029</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
           <t>CP-NAV-085</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t>La API confirma la clave del gasto reintentado por pantalla</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>US-70</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
         <is>
           <t>Resumen</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="10" t="inlineStr">
         <is>
           <t>Planificados</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>Ejecutados (PASSED + FAILED)</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
+      <c r="B195" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados (PASSED + FAILED + DUDA)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="inlineStr">
+        <is>
+          <t>DUDA (pasa, con dudas)</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="inlineStr">
+        <is>
+          <t>% avance (ejecutados/planificados)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
+        <is>
+          <t>% aprobados sobre ejecutados</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>98 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>Por módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>Módulo</t>
+        </is>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>Casos</t>
+        </is>
+      </c>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E206" s="10" t="inlineStr">
+        <is>
+          <t>DUDA</t>
+        </is>
+      </c>
+      <c r="F206" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G206" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DEU-A · Gasto compartido: validaciones de create_transaction (US-34, 018 a 029)</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>13</v>
+      </c>
+      <c r="C207" t="n">
+        <v>12</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DEU-B · Listado, filtro por estado y acceso (US-37 y US-38, 100 a 108C)</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>12</v>
+      </c>
+      <c r="C208" t="n">
+        <v>12</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>DEU-C · Saldar, volver a pendiente y filtro por dirección (US-39, US-40 y US-79, 109 a 127C)</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>28</v>
+      </c>
+      <c r="C209" t="n">
+        <v>28</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>DEU-D · Compartir con varias personas (US-82, 128 a 142B)</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>33</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>33</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DEU-E · Neto de reembolsos en el Resumen (US-30, 143 a 150)</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>9</v>
+      </c>
+      <c r="C211" t="n">
+        <v>8</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DEU-F · Deudas sueltas en el balance del mes (US-83, 151 a 159)</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>10</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1</v>
+      </c>
+      <c r="F212" t="n">
+        <v>9</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>NAV-69 · Barra de navegación (US-69)</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>49</v>
+      </c>
+      <c r="C213" t="n">
+        <v>49</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>NAV-70 · Aviso de guardado y reintento (US-70)</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>36</v>
+      </c>
+      <c r="C214" t="n">
+        <v>34</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>Por prioridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="B217" s="10" t="inlineStr">
+        <is>
+          <t>Casos</t>
+        </is>
+      </c>
+      <c r="C217" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E217" s="10" t="inlineStr">
+        <is>
+          <t>DUDA</t>
+        </is>
+      </c>
+      <c r="F217" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G217" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
         <v>96</v>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
+      <c r="C218" t="n">
+        <v>67</v>
+      </c>
+      <c r="D218" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
+      <c r="E218" t="n">
+        <v>2</v>
+      </c>
+      <c r="F218" t="n">
+        <v>26</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>83</v>
+      </c>
+      <c r="C219" t="n">
+        <v>66</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>16</v>
+      </c>
+      <c r="G219" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>No ejecutados</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>11</v>
+      </c>
+      <c r="C220" t="n">
+        <v>10</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>% avance (ejecutados/planificados)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>98 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>% aprobados sobre ejecutados</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>99 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>Por módulo</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>Módulo</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>Casos</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>No ejecutados</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>DEU · Deudas y gastos compartidos (US-34)</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>13</v>
-      </c>
-      <c r="C114" t="n">
-        <v>12</v>
-      </c>
-      <c r="D114" t="n">
+      <c r="G220" t="n">
         <v>0</v>
       </c>
-      <c r="E114" t="n">
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>Defectos por severidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>Severidad</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>Abiertos</t>
+        </is>
+      </c>
+      <c r="C223" s="10" t="inlineStr">
+        <is>
+          <t>IDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
         <v>1</v>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>NAV-69 · Barra de navegación (US-69)</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>49</v>
-      </c>
-      <c r="C115" t="n">
-        <v>49</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>NAV-70 · Aviso de guardado y reintento (US-70)</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>36</v>
-      </c>
-      <c r="C116" t="n">
-        <v>34</v>
-      </c>
-      <c r="D116" t="n">
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>DEF-029</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>Criterios de salida (docs/07-plan-de-testing.md §6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>Criterio</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr"/>
+      <c r="C230" s="10" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="34" customHeight="1">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>1. Cero defectos de severidad Crítica abiertos</t>
+        </is>
+      </c>
+      <c r="C231" s="12" t="inlineStr">
+        <is>
+          <t>Cumplido</t>
+        </is>
+      </c>
+      <c r="D231" s="11" t="inlineStr">
+        <is>
+          <t>No hay defectos críticos (el único defecto, DEF-029, es de severidad Baja).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="49" customHeight="1">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>2. Cero defectos de severidad Alta abiertos, o justificados por el PO</t>
+        </is>
+      </c>
+      <c r="C232" s="12" t="inlineStr">
+        <is>
+          <t>Cumplido</t>
+        </is>
+      </c>
+      <c r="D232" s="11" t="inlineStr">
+        <is>
+          <t>No hay defectos de severidad Alta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="94" customHeight="1">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>3. Todos los casos de prioridad Alta ejecutados</t>
+        </is>
+      </c>
+      <c r="C233" s="13" t="inlineStr">
+        <is>
+          <t>No cumplido</t>
+        </is>
+      </c>
+      <c r="D233" s="11" t="inlineStr">
+        <is>
+          <t>70 de 96 casos de prioridad Alta ejecutados. No ejecutados: 26, todos BLOCKED porque dependen de funciones todavía no implementadas (US-82, issue #270, y US-83, issue #271): 029, 128, 129, 131, 132, 133, 134, 136, 136C, 136D, 136E, 137, 139, 140, 141, 142, 142A, 142B, 151, 152, 153, 154, 155, 156, 157, 159.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="64" customHeight="1">
+      <c r="A234" s="11" t="inlineStr">
+        <is>
+          <t>4. Toda invariante del alcance con al menos un caso ejecutado</t>
+        </is>
+      </c>
+      <c r="C234" s="14" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="D234" s="11" t="inlineStr">
+        <is>
+          <t>Con casos ejecutados: I1, I10, I18, I2, I3, I4, I7, I9. Solo con casos sin ejecutar: I5. Este reporte cubre Deudas (018 a 029 y 100 a 159) y Navegación; las demás invariantes de V2 (suscripciones, importar, etc.) están en otros casos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="49" customHeight="1">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>5. Regresión de V1 ejecutada y defectos corregidos confirmados</t>
+        </is>
+      </c>
+      <c r="C235" s="15" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="D235" s="11" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de este reporte: la selección de regresión (03) y la confirmación de los defectos de V1 se informan aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="inlineStr">
+        <is>
+          <t>Desvíos respecto de lo planificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="49" customHeight="1">
+      <c r="A238" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>Por prioridad</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>Casos</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
-        <is>
-          <t>No ejecutados</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>43</v>
-      </c>
-      <c r="C120" t="n">
-        <v>41</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>55</v>
-      </c>
-      <c r="C121" t="n">
-        <v>54</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>Defectos por severidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>Severidad</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>Abiertos</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>IDs</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>1</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>DEF-029</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>Criterios de salida (docs/07-plan-de-testing.md §6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="9" t="inlineStr">
-        <is>
-          <t>Criterio</t>
-        </is>
-      </c>
-      <c r="B131" s="9" t="inlineStr"/>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>Detalle</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="34" customHeight="1">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>1. Cero defectos de severidad Crítica abiertos</t>
-        </is>
-      </c>
-      <c r="C132" s="11" t="inlineStr">
-        <is>
-          <t>Cumplido</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>No hay defectos críticos (el único defecto, DEF-029, es de severidad Baja).</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="49" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>2. Cero defectos de severidad Alta abiertos, o justificados por el PO</t>
-        </is>
-      </c>
-      <c r="C133" s="11" t="inlineStr">
-        <is>
-          <t>Cumplido</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>No hay defectos de severidad Alta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="49" customHeight="1">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>3. Todos los casos de prioridad Alta ejecutados</t>
-        </is>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>No cumplido</t>
-        </is>
-      </c>
-      <c r="D134" s="10" t="inlineStr">
-        <is>
-          <t>42 de 43 casos de prioridad Alta ejecutados. Falta: CP-DEU-029. CP-DEU-029 está BLOCKED porque US-82 no está implementada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="49" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>4. Toda invariante del alcance con al menos un caso ejecutado</t>
-        </is>
-      </c>
-      <c r="C135" s="13" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Con casos ejecutados: I1, I10, I18, I2, I4, I7. Este reporte cubre solo Deudas 018–029 y Navegación; las demás invariantes de V2 (deudas y suscripciones) están en otros casos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="49" customHeight="1">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>5. Regresión de V1 ejecutada y defectos corregidos confirmados</t>
-        </is>
-      </c>
-      <c r="C136" s="14" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Fuera del alcance de este reporte: la selección de regresión (03) y la confirmación de los defectos de V1 se informan aparte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Desvíos respecto de lo planificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="49" customHeight="1">
-      <c r="A139" t="n">
-        <v>1</v>
-      </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t>Alcance parcial de V2. Este reporte cubre solo los casos CP-DEU-018 a 029 (Deudas) y CP-NAV-001 a 085 (Navegación). Los otros casos de Deudas (CP-DEU-001 a 017 y 030 en adelante) y los de Suscripciones, Export, Importar y Dashboard no están incluidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="64" customHeight="1">
-      <c r="A140" t="n">
+      <c r="B238" s="11" t="inlineStr">
+        <is>
+          <t>Alcance parcial de V2. Este reporte cubre CP-DEU-018 a 029 y CP-DEU-100 a 159 (Deudas) y CP-NAV-001 a 085 (Navegación): 190 casos. Los otros casos de Deudas (CP-DEU-001 a 017, 030 a 099) y los de Suscripciones, Export, Importar y Dashboard no están incluidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="64" customHeight="1">
+      <c r="A239" t="n">
         <v>2</v>
       </c>
-      <c r="B140" s="10" t="inlineStr">
-        <is>
-          <t>Dos formas de ejecutar. 40 casos de Navegación y los 12 de Deudas (018 a 028) los ejecutó Santiago a mano en el deploy de Vercel, con Chrome. Los otros 44 de Navegación los ejecutó Claude Code en el entorno local (Playwright y el navegador integrado), porque el equipo no los había podido probar. La propiedad cruzada del plan (07-plan-de-testing §1) no se aplicó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="64" customHeight="1">
-      <c r="A141" t="n">
+      <c r="B239" s="11" t="inlineStr">
+        <is>
+          <t>Tres formas de ejecutar. 40 casos de Navegación y los 12 de Deudas (018 a 028) los ejecutó Santiago a mano en el deploy de Vercel, con Chrome. Los otros 44 de Navegación, CP-DEU-029 y los 92 de Deudas del 100 en adelante los ejecutó Claude Code en el entorno local (Playwright, navegador integrado y pedidos directos a la API). La propiedad cruzada del plan (07-plan-de-testing §1) no se aplicó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="64" customHeight="1">
+      <c r="A240" t="n">
         <v>3</v>
       </c>
-      <c r="B141" s="10" t="inlineStr">
+      <c r="B240" s="11" t="inlineStr">
         <is>
           <t>Deudas 018–028 se verificaron en la pantalla, no por API. Los casos están escritos como llamadas directas a create_transaction con varias personas (US-82), que todavía no existe (issue #270). Se ejecutó la prueba equivalente en Registrar («Gasto compartido») de cada caso gemelo; el resultado esperado de la pantalla es el mensaje de error y el botón «Guardar gasto» deshabilitado.</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="49" customHeight="1">
-      <c r="A142" t="n">
+    <row r="241" ht="64" customHeight="1">
+      <c r="A241" t="n">
         <v>4</v>
       </c>
-      <c r="B142" s="10" t="inlineStr">
-        <is>
-          <t>CP-DEU-029 BLOCKED. Como está escrito da 404 «función no encontrada». Con la función actual de una sola persona, sin sesión se responde 401 con el código 42501, o sea que el objetivo de seguridad se cumple, pero el caso no puede darse por ejecutado hasta que exista la función de US-82.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="19" customHeight="1">
-      <c r="A143" t="n">
+      <c r="B241" s="11" t="inlineStr">
+        <is>
+          <t>Funciones todavía no implementadas. US-82 (compartir con varias personas, issue #270) y US-83 (deudas sueltas en el balance del mes, issue #271) no existen en la app: quedan BLOCKED CP-DEU-029, los 33 casos CP-DEU-128 a 142B y los 9 casos CP-DEU-151 a 157 y 159 (43 en total). Se comprobó la ausencia de cada función (botones, respuesta de la API y Resumen) y no se les abrió defecto: dependen de historias pendientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="49" customHeight="1">
+      <c r="A242" t="n">
         <v>5</v>
       </c>
-      <c r="B143" s="10" t="inlineStr">
+      <c r="B242" s="11" t="inlineStr">
+        <is>
+          <t>CP-DEU-145 y CP-DEU-158 con dudas. En el 145 la preparación del caso pide 12 cuotas con la cuenta «Efectivo» y la app solo permite cuotas con tarjeta de crédito (se ejecutó con «Tarjeta de crédito»: el resultado es el esperado): parece un error del caso. El 158 se cumple, pero también se cumpliría sin US-83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="49" customHeight="1">
+      <c r="A243" t="n">
+        <v>6</v>
+      </c>
+      <c r="B243" s="11" t="inlineStr">
+        <is>
+          <t>Preparación por API. En los casos CP-DEU-100 a 159 las deudas, gastos y tipos de cambio de la preparación se cargaron por API (create_debt, create_transaction, settle_debt, delete_transaction, upsert_fx_rate), como en los casos originales con PR-04; el formulario «Nueva deuda» no se ejercitó en esos casos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="19" customHeight="1">
+      <c r="A244" t="n">
+        <v>7</v>
+      </c>
+      <c r="B244" s="11" t="inlineStr">
         <is>
           <t>CP-NAV-060 sin ejecutar: necesita un Pixel 7 con Android 15 y TalkBack en español.</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="34" customHeight="1">
-      <c r="A144" t="n">
-        <v>6</v>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
+    <row r="245" ht="34" customHeight="1">
+      <c r="A245" t="n">
+        <v>8</v>
+      </c>
+      <c r="B245" s="11" t="inlineStr">
         <is>
           <t>CP-NAV-084 FAILED por una diferencia entre el caso y la implementación (204 sin cuerpo en vez de 200 con null). Parece un error del caso. No se corrigió nada: hay que decidir si cambia el caso o la función (DEF-029).</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="79" customHeight="1">
-      <c r="A145" t="n">
-        <v>7</v>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>Adaptaciones de DevTools en las ejecuciones de Claude Code: el corte de red y el perfil de 20 s se aplicaron con el protocolo de Chrome (el mismo mecanismo de Network); en 013 a 017 se ocultó la barra de desplazamiento clásica del navegador integrado para imitar un celular. CP-NAV-041 usó una barrera en Node en lugar del script de PowerShell. CP-NAV-059 verifica la variante mensual equivalente (H-NAV-02) y los casos de «aviso al recargar» etc. se ejecutaron tal cual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="34" customHeight="1">
-      <c r="A146" t="n">
-        <v>8</v>
-      </c>
-      <c r="B146" s="10" t="inlineStr">
+    <row r="246" ht="64" customHeight="1">
+      <c r="A246" t="n">
+        <v>9</v>
+      </c>
+      <c r="B246" s="11" t="inlineStr">
+        <is>
+          <t>Adaptaciones de DevTools en las ejecuciones de Claude Code: el corte de red y el perfil de 20 s se aplicaron con el protocolo de Chrome (el mismo mecanismo de Network); en 013 a 017 se ocultó la barra de desplazamiento clásica del navegador integrado para imitar un celular. CP-NAV-041 usó una barrera en Node en lugar del script de PowerShell. CP-NAV-059 verifica la variante mensual equivalente (H-NAV-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="34" customHeight="1">
+      <c r="A247" t="n">
+        <v>10</v>
+      </c>
+      <c r="B247" s="11" t="inlineStr">
         <is>
           <t>Evidencia: no se adjuntaron capturas al repositorio; lo observado queda en «Resultado obtenido» de cada caso (04-ejecucion).</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="8" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="9" t="inlineStr">
         <is>
           <t>Condiciones de la ejecución</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="34" customHeight="1">
-      <c r="A149" s="9" t="inlineStr">
+    <row r="250" ht="34" customHeight="1">
+      <c r="A250" s="10" t="inlineStr">
         <is>
           <t>Versión probada</t>
         </is>
       </c>
-      <c r="B149" s="10" t="inlineStr">
+      <c r="B250" s="11" t="inlineStr">
         <is>
           <t>Ejecución manual: deploy de Vercel (https://biyu-rust.vercel.app). Ejecución de Claude Code: main en f096e22 (local, con todas las migraciones hasta 20261012000000).</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="34" customHeight="1">
-      <c r="A150" s="9" t="inlineStr">
+    <row r="251" ht="34" customHeight="1">
+      <c r="A251" s="10" t="inlineStr">
         <is>
           <t>Entorno</t>
         </is>
       </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t>Manual: Google Chrome contra el deploy. Claude Code: Vite local (127.0.0.1:5173) + Supabase local; Chromium (Playwright 1.63) y navegador integrado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="19" customHeight="1">
-      <c r="A151" s="9" t="inlineStr">
+      <c r="B251" s="11" t="inlineStr">
+        <is>
+          <t>Manual: Google Chrome contra el deploy. Claude Code: Vite local (127.0.0.1:5173) + Supabase local; Chromium (Playwright 1.63) y navegador integrado; pedidos directos a la API con el token del usuario de prueba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="19" customHeight="1">
+      <c r="A252" s="10" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B151" s="10" t="inlineStr">
+      <c r="B252" s="11" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="19" customHeight="1">
-      <c r="A152" s="9" t="inlineStr">
+    <row r="253" ht="34" customHeight="1">
+      <c r="A253" s="10" t="inlineStr">
         <is>
           <t>Ejecutó</t>
         </is>
       </c>
-      <c r="B152" s="10" t="inlineStr">
-        <is>
-          <t>Santiago (a mano) y Claude Code, supervisado por Santiago.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="34" customHeight="1">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="B253" s="11" t="inlineStr">
+        <is>
+          <t>Santiago (a mano: Deudas 018 a 028 y 40 casos de Navegación) y Claude Code, supervisado por Santiago (el resto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="34" customHeight="1">
+      <c r="A254" s="10" t="inlineStr">
         <is>
           <t>Datos</t>
         </is>
       </c>
-      <c r="B153" s="10" t="inlineStr">
+      <c r="B254" s="11" t="inlineStr">
         <is>
           <t>Usuarios qa+&lt;id del caso&gt;-001@example.com y montos ficticios, uno por caso; en local se pueden borrar con «supabase db reset».</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="B151:G151"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="D133:G133"/>
-    <mergeCell ref="D132:G132"/>
-    <mergeCell ref="B146:G146"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="B143:G143"/>
-    <mergeCell ref="B139:G139"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="B142:G142"/>
+  <mergeCells count="26">
+    <mergeCell ref="B253:G253"/>
+    <mergeCell ref="D235:G235"/>
+    <mergeCell ref="A232:B232"/>
+    <mergeCell ref="B244:G244"/>
+    <mergeCell ref="B240:G240"/>
+    <mergeCell ref="D232:G232"/>
+    <mergeCell ref="B250:G250"/>
+    <mergeCell ref="D231:G231"/>
+    <mergeCell ref="B245:G245"/>
+    <mergeCell ref="B243:G243"/>
+    <mergeCell ref="B246:G246"/>
+    <mergeCell ref="B254:G254"/>
+    <mergeCell ref="A233:B233"/>
+    <mergeCell ref="B239:G239"/>
+    <mergeCell ref="B241:G241"/>
+    <mergeCell ref="D233:G233"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B144:G144"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="B153:G153"/>
-    <mergeCell ref="D136:G136"/>
-    <mergeCell ref="B141:G141"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="B150:G150"/>
-    <mergeCell ref="D135:G135"/>
-    <mergeCell ref="B140:G140"/>
-    <mergeCell ref="B149:G149"/>
-    <mergeCell ref="D134:G134"/>
-    <mergeCell ref="B152:G152"/>
+    <mergeCell ref="B251:G251"/>
+    <mergeCell ref="A235:B235"/>
+    <mergeCell ref="A234:B234"/>
+    <mergeCell ref="B242:G242"/>
+    <mergeCell ref="A231:B231"/>
+    <mergeCell ref="D234:G234"/>
+    <mergeCell ref="B252:G252"/>
+    <mergeCell ref="B238:G238"/>
+    <mergeCell ref="B247:G247"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -560,7 +560,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-005</t>
+          <t>CP-DEU-001</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -570,27 +570,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>No se puede compartir un gasto si falta cuánto te deben</t>
+          <t>El interruptor «Gasto compartido» se enciende y se apaga, y el gasto se guarda sin deuda</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>US-34, US-82</t>
+          <t>US-34</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>DUDA</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -598,7 +598,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-006</t>
+          <t>CP-DEU-002</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>No se puede compartir un gasto si falta con quién</t>
+          <t>Gasto compartido de $120.000,00 en 12 cuotas: se guarda el gasto y la deuda vinculada de Sofía</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>US-34, US-82</t>
+          <t>US-34, US-35, US-82</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>DUDA</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H4" s="3" t="n"/>
@@ -636,7 +636,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-007</t>
+          <t>CP-DEU-003</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Un ingreso no se puede compartir</t>
+          <t>Gasto compartido en dólares (US$100 a tipo de cambio 1250): avisa en dólares y congela el tipo de cambio</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>US-34, US-82</t>
+          <t>US-34</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>DUDA</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
@@ -674,22 +674,22 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-008</t>
+          <t>CP-DEU-004</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>El nombre hecho solo de espacios no cuenta como nombre</t>
+          <t>El monto adeudado vacío muestra «Ingresá cuánto te debe» y no deja guardar</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>US-34, US-82</t>
+          <t>US-34</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H6" s="3" t="n"/>
@@ -712,17 +712,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-009</t>
+          <t>CP-DEU-005</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>El nombre admite hasta 60 caracteres, no 61</t>
+          <t>No se puede compartir un gasto si falta cuánto te deben</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-010</t>
+          <t>CP-DEU-006</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>No se puede deber 0 pesos</t>
+          <t>No se puede compartir un gasto si falta con quién</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-015</t>
+          <t>CP-DEU-007</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Eliminar el gasto vinculado oculta la deuda de /debts, deja de sumarla en "Te deben" y en el neto del Resumen, y conserva intacta su fila en debts</t>
+          <t>Un ingreso no se puede compartir</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>US-30, US-35, US-37</t>
+          <t>US-34, US-82</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H9" s="3" t="n"/>
@@ -826,7 +826,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-016</t>
+          <t>CP-DEU-008</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Al restaurar desde Movimientos → Eliminados un gasto cuya deuda vinculada estaba saldada, la deuda vuelve a /debts con estado saldada y la misma fecha settled_at</t>
+          <t>El nombre hecho solo de espacios no cuenta como nombre</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>US-35</t>
+          <t>US-34, US-82</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H10" s="3" t="n"/>
@@ -864,27 +864,27 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-017</t>
+          <t>CP-DEU-009</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Estado inicial de /debts/new y guardado de una deuda "Me deben" en ARS por $20.000,00 crea una fila pendiente con transaction_id = null en una sola llamada a create_debt</t>
+          <t>El nombre admite hasta 60 caracteres, no 61</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-34, US-82</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H11" s="3" t="n"/>
@@ -902,7 +902,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-019</t>
+          <t>CP-DEU-010</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>En /debts/new, elegir "US$" con TC de referencia de 1250 precompleta "1.250,00", muestra "≈ $50.000,00" para US$40 y guarda fx_rate = 1250.0000 y amount_ars = 50000.00</t>
+          <t>No se puede deber 0 pesos</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-34, US-82</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H12" s="3" t="n"/>
@@ -940,32 +940,32 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-023</t>
+          <t>CP-DEU-011</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>En /debts/new, un "Monto" con más de 2 decimales ("0,001") muestra "El monto admite hasta 2 decimales"</t>
+          <t>Una deuda igual al gasto se acepta: «Tu parte» queda en $0,00</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-41</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>DUDA</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-024</t>
+          <t>CP-DEU-012</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>En /debts/new con US$, Monto = 0,01 y TC = 0,5 se acepta (redondeo half-up a $0,01) y guarda amount_ars = "0.01"</t>
+          <t>Una deuda un centavo mayor que el gasto no se puede guardar</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-41</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1001,9 +1001,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1011,16 +1011,12 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>DEF-037</t>
-        </is>
-      </c>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-026</t>
+          <t>CP-DEU-013</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1030,12 +1026,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>En /debts/new, una fecha posterior a hoy (&lt;MAÑANA&gt;) muestra "La fecha no puede ser futura" y deshabilita "Guardar deuda"</t>
+          <t>Por API, una deuda mayor que el gasto se rechaza y no se guarda nada</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-41, US-82</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1045,7 +1041,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1058,7 +1054,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-027</t>
+          <t>CP-DEU-015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1068,17 +1064,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_person = "" se rechaza con "Ingresá el nombre de la persona"</t>
+          <t>Eliminar el gasto vinculado oculta la deuda de /debts, deja de sumarla en "Te deben" y en el neto del Resumen, y conserva intacta su fila en debts</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-30, US-35, US-37</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1096,22 +1092,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-028</t>
+          <t>CP-DEU-016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_person de 61 caracteres se rechaza con "La persona admite hasta 60 caracteres"</t>
+          <t>Al restaurar desde Movimientos → Eliminados un gasto cuya deuda vinculada estaba saldada, la deuda vuelve a /debts con estado saldada y la misma fecha settled_at</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>US-36</t>
+          <t>US-35</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1134,7 +1130,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-029</t>
+          <t>CP-DEU-017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1144,7 +1140,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_amount = 0 se rechaza con "I4: el monto debe ser mayor a cero"</t>
+          <t>Estado inicial de /debts/new y guardado de una deuda "Me deben" en ARS por $20.000,00 crea una fila pendiente con transaction_id = null en una sola llamada a create_debt</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1154,7 +1150,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1172,17 +1168,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-030</t>
+          <t>CP-DEU-019</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_amount = 1.001 (literal JSON) se rechaza con "I4: el monto admite hasta 2 decimales"</t>
+          <t>En /debts/new, elegir "US$" con TC de referencia de 1250 precompleta "1.250,00", muestra "≈ $50.000,00" para US$40 y guarda fx_rate = 1250.0000 y amount_ars = 50000.00</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1192,7 +1188,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1210,17 +1206,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-031</t>
+          <t>CP-DEU-023</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_currency = "USD" con p_fx_rate = null se rechaza con "I5: fx_rate es obligatorio si y solo si la moneda es USD"</t>
+          <t>En /debts/new, un "Monto" con más de 2 decimales ("0,001") muestra "El monto admite hasta 2 decimales"</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1248,17 +1244,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-032</t>
+          <t>CP-DEU-024</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_currency = "ARS" con p_fx_rate = "1250.0000" se rechaza con "I5: fx_rate es obligatorio si y solo si la moneda es USD"</t>
+          <t>En /debts/new con US$, Monto = 0,01 y TC = 0,5 se acepta (redondeo half-up a $0,01) y guarda amount_ars = "0.01"</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1271,9 +1267,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1281,12 +1277,16 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>DEF-037</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-033</t>
+          <t>CP-DEU-025</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt, p_incurred_on = "&lt;MAÑANA&gt;" se rechaza con "La fecha no puede ser posterior a hoy"</t>
+          <t>En «Nueva deuda» con US$, un tipo de cambio de 0 muestra «El tipo de cambio debe ser mayor a cero»</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1319,12 +1319,16 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>DEF-037</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-034</t>
+          <t>CP-DEU-026</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Directo contra create_debt con el rol anon (sin Authorization) responde 42501 (permission denied)</t>
+          <t>En /debts/new, una fecha posterior a hoy (&lt;MAÑANA&gt;) muestra "La fecha no puede ser futura" y deshabilita "Guardar deuda"</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1362,7 +1366,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-035</t>
+          <t>CP-DEU-027</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1372,7 +1376,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Un POST /rest/v1/debts directo con sesión autenticada responde 42501 (permission denied) y no crea filas</t>
+          <t>Directo contra create_debt, p_person = "" se rechaza con "Ingresá el nombre de la persona"</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1400,22 +1404,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-040</t>
+          <t>CP-DEU-028</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Un filtro inválido en la dirección se trata como «Pendientes»</t>
+          <t>Directo contra create_debt, p_person de 61 caracteres se rechaza con "La persona admite hasta 60 caracteres"</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>US-38</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1438,22 +1442,22 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-041</t>
+          <t>CP-DEU-029</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Deudas pendientes: la de fecha más nueva va primero</t>
+          <t>Directo contra create_debt, p_amount = 0 se rechaza con "I4: el monto debe ser mayor a cero"</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>US-38</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1476,7 +1480,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-042</t>
+          <t>CP-DEU-030</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1486,12 +1490,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Sin deudas pendientes: mensaje y botón «Cargar una deuda»</t>
+          <t>Directo contra create_debt, p_amount = 1.001 (literal JSON) se rechaza con "I4: el monto admite hasta 2 decimales"</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>US-38</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1514,7 +1518,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-043</t>
+          <t>CP-DEU-031</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1524,12 +1528,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Otro usuario no ve las deudas de alguien más</t>
+          <t>Directo contra create_debt, p_currency = "USD" con p_fx_rate = null se rechaza con "I5: fx_rate es obligatorio si y solo si la moneda es USD"</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>US-38</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1552,22 +1556,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-044</t>
+          <t>CP-DEU-032</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Por API, otro usuario no recibe las deudas de alguien más</t>
+          <t>Directo contra create_debt, p_currency = "ARS" con p_fx_rate = "1250.0000" se rechaza con "I5: fx_rate es obligatorio si y solo si la moneda es USD"</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>US-38</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1590,7 +1594,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-045</t>
+          <t>CP-DEU-033</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1600,12 +1604,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Por API, sin sesión no se pueden leer las deudas</t>
+          <t>Directo contra create_debt, p_incurred_on = "&lt;MAÑANA&gt;" se rechaza con "La fecha no puede ser posterior a hoy"</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>US-38</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1628,7 +1632,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-046</t>
+          <t>CP-DEU-034</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1638,17 +1642,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Marcar una deuda como saldada desde «Pendientes»</t>
+          <t>Directo contra create_debt con el rol anon (sin Authorization) responde 42501 (permission denied)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>US-30, US-37, US-39</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1666,7 +1670,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-047</t>
+          <t>CP-DEU-035</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1676,12 +1680,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>«Deshacer» devuelve la deuda a pendiente</t>
+          <t>Un POST /rest/v1/debts directo con sesión autenticada responde 42501 (permission denied) y no crea filas</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>US-39</t>
+          <t>US-36</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1704,22 +1708,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-048</t>
+          <t>CP-DEU-040</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Saldar una deuda que ya se saldó en otra pestaña muestra un error</t>
+          <t>Un filtro inválido en la dirección se trata como «Pendientes»</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>US-39</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1742,22 +1746,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-049</t>
+          <t>CP-DEU-041</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Por API, saldar una deuda ya saldada se rechaza</t>
+          <t>Deudas pendientes: la de fecha más nueva va primero</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>US-39</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1780,22 +1784,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-050</t>
+          <t>CP-DEU-042</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Por API, un usuario no puede saldar la deuda de otro</t>
+          <t>Sin deudas pendientes: mensaje y botón «Cargar una deuda»</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>US-39</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1818,7 +1822,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-051</t>
+          <t>CP-DEU-043</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1828,12 +1832,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Por API, no se puede modificar una deuda directamente</t>
+          <t>Otro usuario no ve las deudas de alguien más</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>US-39</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1856,7 +1860,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-052</t>
+          <t>CP-DEU-044</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1866,17 +1870,17 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>«Volver a pendiente» desde «Saldadas»</t>
+          <t>Por API, otro usuario no recibe las deudas de alguien más</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>US-40</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1894,22 +1898,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-053</t>
+          <t>CP-DEU-045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Saldar y reabrir tres veces seguidas deja la deuda pendiente</t>
+          <t>Por API, sin sesión no se pueden leer las deudas</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>US-40</t>
+          <t>US-38</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1932,7 +1936,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-054</t>
+          <t>CP-DEU-046</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1942,12 +1946,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Filtro por dirección: «Todas», «Te deben» y «Debés»</t>
+          <t>Marcar una deuda como saldada desde «Pendientes»</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>US-79</t>
+          <t>US-30, US-37, US-39</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1970,7 +1974,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-055</t>
+          <t>CP-DEU-047</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1980,22 +1984,22 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Gasto compartido con varias personas: agregar, quitar y guardar</t>
+          <t>«Deshacer» devuelve la deuda a pendiente</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>US-82</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2008,22 +2012,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-056</t>
+          <t>CP-DEU-048</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Se puede compartir con hasta 10 personas</t>
+          <t>Saldar una deuda que ya se saldó en otra pestaña muestra un error</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>US-82</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2031,9 +2035,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2046,7 +2050,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-057</t>
+          <t>CP-DEU-049</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2056,12 +2060,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Por API, deudas que suman más que el gasto se rechazan</t>
+          <t>Por API, saldar una deuda ya saldada se rechaza</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>US-82</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2069,9 +2073,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2084,7 +2088,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-058</t>
+          <t>CP-DEU-050</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2094,17 +2098,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Resumen: gasto bruto y neto de reembolsos</t>
+          <t>Por API, un usuario no puede saldar la deuda de otro</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>US-30</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2122,7 +2126,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-059</t>
+          <t>CP-DEU-051</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2132,17 +2136,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Resumen: el neto no cambia al saldar la deuda</t>
+          <t>Por API, no se puede modificar una deuda directamente</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>US-30</t>
+          <t>US-39</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2160,7 +2164,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-060</t>
+          <t>CP-DEU-052</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2170,17 +2174,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Resumen: una deuda suelta «Me deben» no cambia el neto</t>
+          <t>«Volver a pendiente» desde «Saldadas»</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>US-30</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2198,27 +2202,27 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CP-DEU-061</t>
+          <t>CP-DEU-053</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Resumen: el neto en dólares no cambia si cambia el tipo de cambio</t>
+          <t>Saldar y reabrir tres veces seguidas deja la deuda pendiente</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>US-30</t>
+          <t>US-40</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2236,22 +2240,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-001</t>
+          <t>CP-DEU-054</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>La barra tiene cuatro secciones en el orden correcto</t>
+          <t>Filtro por dirección: «Todas», «Te deben» y «Debés»</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-79</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2266,7 +2270,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H47" s="3" t="n"/>
@@ -2274,22 +2278,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-002</t>
+          <t>CP-DEU-055</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>«Deudas» lleva a Deudas</t>
+          <t>Gasto compartido con varias personas: agregar, quitar y guardar</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2297,14 +2301,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H48" s="3" t="n"/>
@@ -2312,37 +2316,37 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-003</t>
+          <t>CP-DEU-056</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>En el Resumen la barra marca «Resumen»</t>
+          <t>Se puede compartir con hasta 10 personas</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H49" s="3" t="n"/>
@@ -2350,37 +2354,37 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-004</t>
+          <t>CP-DEU-057</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>En Ajustes no se marca ninguna de las cuatro secciones</t>
+          <t>Por API, deudas que suman más que el gasto se rechazan</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-82</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H50" s="3" t="n"/>
@@ -2388,27 +2392,27 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-005</t>
+          <t>CP-DEU-058</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Ancho 1023 px: barra abajo y engranaje de Ajustes</t>
+          <t>Resumen: gasto bruto y neto de reembolsos</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2426,27 +2430,27 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-006</t>
+          <t>CP-DEU-059</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Ancho 1024 px: barra lateral con Ajustes al pie</t>
+          <t>Resumen: el neto no cambia al saldar la deuda</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2464,27 +2468,27 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-007</t>
+          <t>CP-DEU-060</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Identificadores únicos en Registrar (375 px)</t>
+          <t>Resumen: una deuda suelta «Me deben» no cambia el neto</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2502,22 +2506,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-008</t>
+          <t>CP-DEU-061</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>«Ver todos» y «‹ Resumen» mantienen el mes</t>
+          <t>Resumen: el neto en dólares no cambia si cambia el tipo de cambio</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>US-69</t>
+          <t>US-30</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2532,7 +2536,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H54" s="3" t="n"/>
@@ -2540,7 +2544,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-009</t>
+          <t>CP-NAV-001</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2550,7 +2554,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Deudas no arrastra el mes del Resumen</t>
+          <t>La barra tiene cuatro secciones en el orden correcto</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2578,17 +2582,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-010</t>
+          <t>CP-NAV-002</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Tocar «Registrar» estando en Registrar no pierde lo cargado</t>
+          <t>«Deudas» lleva a Deudas</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2616,7 +2620,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-011</t>
+          <t>CP-NAV-003</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2626,12 +2630,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Guardar $12.500 muestra la confirmación completa</t>
+          <t>En el Resumen la barra marca «Resumen»</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>US-10, US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2654,27 +2658,27 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-012</t>
+          <t>CP-NAV-004</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Sin internet el gasto no se pierde y aparece «Reintentar»</t>
+          <t>En Ajustes no se marca ninguna de las cuatro secciones</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2692,27 +2696,27 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-013</t>
+          <t>CP-NAV-005</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Reintentar al volver internet guarda una sola vez</t>
+          <t>Ancho 1023 px: barra abajo y engranaje de Ajustes</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H59" s="3" t="n"/>
@@ -2730,22 +2734,22 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-014</t>
+          <t>CP-NAV-006</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Con internet muy lenta, a los 15 segundos avisa que falló</t>
+          <t>Ancho 1024 px: barra lateral con Ajustes al pie</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2768,22 +2772,22 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-015</t>
+          <t>CP-NAV-007</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Reintentar no duplica un gasto que ya se había guardado</t>
+          <t>Identificadores únicos en Registrar (375 px)</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2806,22 +2810,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-016</t>
+          <t>CP-NAV-008</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>La misma clave dos veces seguidas devuelve el mismo gasto</t>
+          <t>«Ver todos» y «‹ Resumen» mantienen el mes</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2836,7 +2840,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H62" s="3" t="n"/>
@@ -2844,22 +2848,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-017</t>
+          <t>CP-NAV-009</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Dos pedidos simultáneos con la misma clave crean un solo gasto</t>
+          <t>Deudas no arrastra el mes del Resumen</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2874,7 +2878,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H63" s="3" t="n"/>
@@ -2882,7 +2886,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-018</t>
+          <t>CP-NAV-010</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2892,12 +2896,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>La misma clave en dos usuarios distintos no se pisa</t>
+          <t>Tocar «Registrar» estando en Registrar no pierde lo cargado</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-69</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -2912,7 +2916,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H64" s="3" t="n"/>
@@ -2920,27 +2924,27 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-019</t>
+          <t>CP-NAV-011</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Si se archiva la categoría antes de guardar, el gasto se rechaza con aviso</t>
+          <t>Guardar $12.500 muestra la confirmación completa</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>US-70</t>
+          <t>US-10, US-70</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2958,7 +2962,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-020</t>
+          <t>CP-NAV-012</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2968,7 +2972,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>La API rechaza un gasto con una categoría archivada</t>
+          <t>Sin internet el gasto no se pierde y aparece «Reintentar»</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H66" s="3" t="n"/>
@@ -2996,7 +3000,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-021</t>
+          <t>CP-NAV-013</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3006,7 +3010,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Al volver a Registrar aparece el gasto pendiente</t>
+          <t>Reintentar al volver internet guarda una sola vez</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -3034,7 +3038,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-022</t>
+          <t>CP-NAV-014</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3044,7 +3048,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Recuperar un gasto que en realidad ya estaba guardado</t>
+          <t>Con internet muy lenta, a los 15 segundos avisa que falló</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3054,7 +3058,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3072,7 +3076,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-023</t>
+          <t>CP-NAV-015</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3082,7 +3086,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Descartar borra el pendiente, incluso al recargar</t>
+          <t>Reintentar no duplica un gasto que ya se había guardado</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -3102,7 +3106,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H69" s="3" t="n"/>
@@ -3110,7 +3114,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-024</t>
+          <t>CP-NAV-016</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3120,7 +3124,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión borra los pendientes</t>
+          <t>La misma clave dos veces seguidas devuelve el mismo gasto</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -3140,7 +3144,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H70" s="3" t="n"/>
@@ -3148,7 +3152,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>CP-NAV-025</t>
+          <t>CP-NAV-017</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3158,7 +3162,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Tocar dos veces «Guardar» guarda una sola vez</t>
+          <t>Dos pedidos simultáneos con la misma clave crean un solo gasto</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -3168,7 +3172,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3178,7 +3182,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H71" s="3" t="n"/>
@@ -3186,22 +3190,22 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-001</t>
+          <t>CP-NAV-018</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Una URL válida fija septiembre 2026</t>
+          <t>La misma clave en dos usuarios distintos no se pisa</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3224,7 +3228,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-002</t>
+          <t>CP-NAV-019</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3234,12 +3238,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>El mes siguiente está bloqueado</t>
+          <t>Si se archiva la categoría antes de guardar, el gasto se rechaza con aviso</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -3254,7 +3258,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H73" s="3" t="n"/>
@@ -3262,7 +3266,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-003</t>
+          <t>CP-NAV-020</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3272,17 +3276,17 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>El alcance mensual propone el nombre 2026-09</t>
+          <t>La API rechaza un gasto con una categoría archivada</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3300,7 +3304,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-004</t>
+          <t>CP-NAV-021</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3310,17 +3314,17 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>El primer día del mes se incluye</t>
+          <t>Al volver a Registrar aparece el gasto pendiente</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3330,7 +3334,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H75" s="3" t="n"/>
@@ -3338,7 +3342,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-005</t>
+          <t>CP-NAV-022</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3348,17 +3352,17 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>El día posterior al mes se excluye</t>
+          <t>Recuperar un gasto que en realidad ya estaba guardado</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3376,7 +3380,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-006</t>
+          <t>CP-NAV-023</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3386,17 +3390,17 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>El 1 de enero se incluye en el año</t>
+          <t>Descartar borra el pendiente, incluso al recargar</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3406,7 +3410,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H77" s="3" t="n"/>
@@ -3414,7 +3418,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-007</t>
+          <t>CP-NAV-024</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3424,17 +3428,17 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>El día posterior al año se excluye</t>
+          <t>Cerrar sesión borra los pendientes</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3444,7 +3448,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H78" s="3" t="n"/>
@@ -3452,7 +3456,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-008</t>
+          <t>CP-NAV-025</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3462,17 +3466,17 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Una transacción eliminada queda fuera</t>
+          <t>Tocar dos veces «Guardar» guarda una sola vez</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>US-47</t>
+          <t>US-70</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3482,7 +3486,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H79" s="3" t="n"/>
@@ -3490,17 +3494,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-009</t>
+          <t>CP-EXP-001</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>El archivo comienza con BOM UTF-8</t>
+          <t>Una URL válida fija septiembre 2026</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3528,7 +3532,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-010</t>
+          <t>CP-EXP-002</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3538,7 +3542,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>El encabezado tiene doce columnas exactas</t>
+          <t>El mes siguiente está bloqueado</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3548,7 +3552,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3566,7 +3570,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-011</t>
+          <t>CP-EXP-003</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3576,7 +3580,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Doce cuotas salen en una sola fila por el total</t>
+          <t>El alcance mensual propone el nombre 2026-09</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3586,7 +3590,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3604,7 +3608,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-012</t>
+          <t>CP-EXP-004</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3614,7 +3618,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>ARS se escribe con dos decimales exactos</t>
+          <t>El primer día del mes se incluye</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3624,7 +3628,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3642,7 +3646,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-013</t>
+          <t>CP-EXP-005</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3652,7 +3656,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>USD conserva cuatro decimales de TC</t>
+          <t>El día posterior al mes se excluye</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3662,7 +3666,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3680,7 +3684,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-014</t>
+          <t>CP-EXP-006</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3690,7 +3694,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Una coma obliga a entrecomillar la descripción</t>
+          <t>El 1 de enero se incluye en el año</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3700,7 +3704,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3718,7 +3722,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-015</t>
+          <t>CP-EXP-007</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3728,7 +3732,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Las comillas internas se duplican</t>
+          <t>El día posterior al año se excluye</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3738,7 +3742,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3756,7 +3760,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-016</t>
+          <t>CP-EXP-008</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3766,7 +3770,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Descripción con igual se neutraliza</t>
+          <t>Una transacción eliminada queda fuera</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3794,7 +3798,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-017</t>
+          <t>CP-EXP-009</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3804,7 +3808,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Una categoría que empieza con igual se neutraliza</t>
+          <t>El archivo comienza con BOM UTF-8</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -3832,7 +3836,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-018</t>
+          <t>CP-EXP-010</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3842,7 +3846,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>1.500 transacciones se exportan sin faltantes</t>
+          <t>El encabezado tiene doce columnas exactas</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3852,7 +3856,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3870,7 +3874,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-019</t>
+          <t>CP-EXP-011</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3880,7 +3884,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>El CSV de A no contiene movimientos de B</t>
+          <t>Doce cuotas salen en una sola fila por el total</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3908,7 +3912,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-020</t>
+          <t>CP-EXP-012</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3918,7 +3922,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>La API con token de A devuelve cero filas de B</t>
+          <t>ARS se escribe con dos decimales exactos</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3946,17 +3950,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-021</t>
+          <t>CP-EXP-013</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Categoría archivada sale con el nombre actual</t>
+          <t>USD conserva cuatro decimales de TC</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3984,17 +3988,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-022</t>
+          <t>CP-EXP-014</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Un ingreso exporta categoría vacía</t>
+          <t>Una coma obliga a entrecomillar la descripción</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -4022,7 +4026,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-023</t>
+          <t>CP-EXP-015</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4032,7 +4036,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Un doble click inicia una sola descarga</t>
+          <t>Las comillas internas se duplican</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -4060,17 +4064,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-024</t>
+          <t>CP-EXP-016</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Un mes sin transacciones muestra Vacío</t>
+          <t>Descripción con igual se neutraliza</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -4080,7 +4084,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -4098,7 +4102,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-025</t>
+          <t>CP-EXP-017</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4108,7 +4112,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Offline muestra el error exacto</t>
+          <t>Una categoría que empieza con igual se neutraliza</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -4118,7 +4122,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -4136,7 +4140,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-026</t>
+          <t>CP-EXP-018</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>El reintento después de Offline descarga completo</t>
+          <t>1.500 transacciones se exportan sin faltantes</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -4174,17 +4178,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-027</t>
+          <t>CP-EXP-019</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Tocar fuera cierra sin descargar</t>
+          <t>El CSV de A no contiene movimientos de B</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -4194,12 +4198,12 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -4207,26 +4211,22 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>DEF-030</t>
-        </is>
-      </c>
+      <c r="H98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-028</t>
+          <t>CP-EXP-020</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Atrás cierra la hoja inicial</t>
+          <t>La API con token de A devuelve cero filas de B</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -4249,26 +4249,22 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>DEF-031</t>
-        </is>
-      </c>
+      <c r="H99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-029</t>
+          <t>CP-EXP-021</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Atrás durante Exportando cancela la descarga</t>
+          <t>Categoría archivada sale con el nombre actual</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -4291,26 +4287,22 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>DEF-032</t>
-        </is>
-      </c>
+      <c r="H100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-030</t>
+          <t>CP-EXP-022</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Una alta concurrente impide descargar un año incompleto</t>
+          <t>Un ingreso exporta categoría vacía</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -4320,7 +4312,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -4338,7 +4330,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>CP-EXP-031</t>
+          <t>CP-EXP-023</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4348,7 +4340,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>HTTP 500 muestra Error y no descarga</t>
+          <t>Un doble click inicia una sola descarga</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -4358,7 +4350,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -4376,7 +4368,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-001</t>
+          <t>CP-EXP-024</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4386,17 +4378,17 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>El acceso desde Registrar abre el paso Archivo</t>
+          <t>Un mes sin transacciones muestra Vacío</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -4414,22 +4406,22 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-002</t>
+          <t>CP-EXP-025</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>A1 rechaza la extensión .xls</t>
+          <t>Offline muestra el error exacto</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -4452,22 +4444,22 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-003</t>
+          <t>CP-EXP-026</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>A2 rechaza 1.048.577 bytes</t>
+          <t>El reintento después de Offline descarga completo</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -4490,32 +4482,32 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-004</t>
+          <t>CP-EXP-027</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>A3 rechaza un archivo dañado con extensión xlsx</t>
+          <t>Tocar fuera cierra sin descargar</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -4523,12 +4515,16 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H106" s="3" t="n"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>DEF-030</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-005</t>
+          <t>CP-EXP-028</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4538,22 +4534,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>A4 enumera tres encabezados obligatorios faltantes</t>
+          <t>Atrás cierra la hoja inicial</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -4561,27 +4557,31 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H107" s="3" t="n"/>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>DEF-031</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-006</t>
+          <t>CP-EXP-029</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>A7 rechaza 501 filas con datos</t>
+          <t>Atrás durante Exportando cancela la descarga</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -4589,9 +4589,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -4599,27 +4599,31 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H108" s="3" t="n"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>DEF-032</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-007</t>
+          <t>CP-EXP-030</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>El límite de filas acepta exactamente 500</t>
+          <t>Una alta concurrente impide descargar un año incompleto</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -4642,27 +4646,27 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-008</t>
+          <t>CP-EXP-031</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Los encabezados aceptan orden, mayúsculas, espacios y tildes distintos</t>
+          <t>HTTP 500 muestra Error y no descarga</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>US-74</t>
+          <t>US-47</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -4680,7 +4684,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-009</t>
+          <t>CP-IMP-001</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4690,17 +4694,17 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>F1: fecha vacía</t>
+          <t>El acceso desde Registrar abre el paso Archivo</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -4718,7 +4722,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-010</t>
+          <t>CP-IMP-002</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4728,12 +4732,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>F2: fecha inexistente</t>
+          <t>A1 rechaza la extensión .xls</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -4756,7 +4760,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-011</t>
+          <t>CP-IMP-003</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4766,12 +4770,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F3: fecha futura fija</t>
+          <t>A2 rechaza 1.048.577 bytes</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -4794,7 +4798,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-012</t>
+          <t>CP-IMP-004</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4804,12 +4808,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F5: tipo inválido</t>
+          <t>A3 rechaza un archivo dañado con extensión xlsx</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -4832,7 +4836,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-013</t>
+          <t>CP-IMP-005</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4842,12 +4846,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F7: monto no numérico</t>
+          <t>A4 enumera tres encabezados obligatorios faltantes</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4870,22 +4874,22 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-014</t>
+          <t>CP-IMP-006</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F8: monto cero</t>
+          <t>A7 rechaza 501 filas con datos</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -4908,7 +4912,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-015</t>
+          <t>CP-IMP-007</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4918,12 +4922,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F9: monto con tres decimales</t>
+          <t>El límite de filas acepta exactamente 500</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -4946,7 +4950,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-016</t>
+          <t>CP-IMP-008</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4956,17 +4960,17 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F12: moneda EUR</t>
+          <t>Los encabezados aceptan orden, mayúsculas, espacios y tildes distintos</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>US-76</t>
+          <t>US-74</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -4984,7 +4988,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-017</t>
+          <t>CP-IMP-009</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4994,7 +4998,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F13a: USD sin tipo de cambio</t>
+          <t>F1: fecha vacía</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -5022,7 +5026,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-018</t>
+          <t>CP-IMP-010</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5032,7 +5036,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F13b: ARS con tipo de cambio</t>
+          <t>F2: fecha inexistente</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -5060,7 +5064,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-019</t>
+          <t>CP-IMP-011</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5070,7 +5074,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F14b: categoría inexistente</t>
+          <t>F3: fecha futura fija</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -5098,7 +5102,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-020</t>
+          <t>CP-IMP-012</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5108,7 +5112,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F14d: cuenta inexistente</t>
+          <t>F5: tipo inválido</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -5136,7 +5140,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-021</t>
+          <t>CP-IMP-013</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5146,7 +5150,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F14e: trece cuotas</t>
+          <t>F7: monto no numérico</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -5174,17 +5178,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-022</t>
+          <t>CP-IMP-014</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>F15: cuotas en cuenta no crédito</t>
+          <t>F8: monto cero</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -5212,7 +5216,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-023</t>
+          <t>CP-IMP-015</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5222,7 +5226,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Errores de varias columnas conservan el orden de reglas</t>
+          <t>F9: monto con tres decimales</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -5250,7 +5254,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-024</t>
+          <t>CP-IMP-016</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5260,7 +5264,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Nombres, tipo y moneda aceptan espacios y mayúsculas</t>
+          <t>F12: moneda EUR</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -5270,12 +5274,12 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -5283,16 +5287,12 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>DEF-033</t>
-        </is>
-      </c>
+      <c r="H126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-025</t>
+          <t>CP-IMP-017</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Categoría archivada no se acepta aunque el nombre coincida</t>
+          <t>F13a: USD sin tipo de cambio</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-026</t>
+          <t>CP-IMP-018</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>El texto 1.500 se interpreta como mil quinientos</t>
+          <t>F13b: ARS con tipo de cambio</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -5368,17 +5368,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-027</t>
+          <t>CP-IMP-019</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>El resumen del archivo de ejemplo suma solo las siete filas listas</t>
+          <t>F14b: categoría inexistente</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-028</t>
+          <t>CP-IMP-020</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>El filtro muestra solo las cuatro filas con error</t>
+          <t>F14d: cuenta inexistente</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-029</t>
+          <t>CP-IMP-021</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Cero filas listas deshabilita Importar 0 movimientos</t>
+          <t>F14e: trece cuotas</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -5482,27 +5482,27 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-030</t>
+          <t>CP-IMP-022</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Confirmar importa solo las filas listas con todos sus campos</t>
+          <t>F15: cuotas en cuenta no crédito</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -5520,27 +5520,27 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-031</t>
+          <t>CP-IMP-023</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>La compra de 240.000 en seis cuotas crea seis imputaciones exactas</t>
+          <t>Errores de varias columnas conservan el orden de reglas</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -5558,32 +5558,32 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-032</t>
+          <t>CP-IMP-024</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Un rechazo tardío de categoría no impide las otras filas</t>
+          <t>Nombres, tipo y moneda aceptan espacios y mayúsculas</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -5591,32 +5591,36 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H134" s="3" t="n"/>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>DEF-033</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-033</t>
+          <t>CP-IMP-025</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Quinientas filas de doce cuotas terminan en menos de diez segundos</t>
+          <t>Categoría archivada no se acepta aunque el nombre coincida</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -5634,27 +5638,27 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-034</t>
+          <t>CP-IMP-026</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>La RPC procesa una válida y rechaza tres inválidas</t>
+          <t>El texto 1.500 se interpreta como mil quinientos</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -5672,7 +5676,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-035</t>
+          <t>CP-IMP-027</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5682,17 +5686,17 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>La RPC rechaza un lote de 501 elementos</t>
+          <t>El resumen del archivo de ejemplo suma solo las siete filas listas</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -5710,27 +5714,27 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-036</t>
+          <t>CP-IMP-028</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>El rol anon no puede ejecutar import_transactions</t>
+          <t>El filtro muestra solo las cuatro filas con error</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -5748,22 +5752,22 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-037</t>
+          <t>CP-IMP-029</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Otro usuario no ve transacciones ni imports ajenos</t>
+          <t>Cero filas listas deshabilita Importar 0 movimientos</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>US-77</t>
+          <t>US-76</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -5786,7 +5790,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-038</t>
+          <t>CP-IMP-030</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5796,12 +5800,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Reintento tras respuesta perdida reconoce lo guardado</t>
+          <t>Confirmar importa solo las filas listas con todos sus campos</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>US-78</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -5824,7 +5828,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-039</t>
+          <t>CP-IMP-031</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5834,12 +5838,12 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Dos llamadas API con el mismo import_id son idempotentes</t>
+          <t>La compra de 240.000 en seis cuotas crea seis imputaciones exactas</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>US-78</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -5862,7 +5866,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-040</t>
+          <t>CP-IMP-032</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5872,12 +5876,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Sin respuesta conserva Revisión</t>
+          <t>Un rechazo tardío de categoría no impide las otras filas</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>US-78</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -5900,7 +5904,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>CP-IMP-041</t>
+          <t>CP-IMP-033</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5910,17 +5914,17 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Sesión vencida ofrece volver a entrar</t>
+          <t>Quinientas filas de doce cuotas terminan en menos de diez segundos</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>US-78</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -5938,7 +5942,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-001</t>
+          <t>CP-IMP-034</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5948,17 +5952,17 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Dar de alta una suscripción en ARS desde hace 2 meses con día de cobro 10 genera los 2 gastos vencidos al guardar</t>
+          <t>La RPC procesa una válida y rechaza tres inválidas</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -5968,7 +5972,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H144" s="3" t="n"/>
@@ -5976,27 +5980,27 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-002</t>
+          <t>CP-IMP-035</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Dar de alta una suscripción en ARS desde el mes siguiente no genera gastos al guardar</t>
+          <t>La RPC rechaza un lote de 501 elementos</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>US-52, US-53, US-61</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -6006,7 +6010,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H145" s="3" t="n"/>
@@ -6014,22 +6018,22 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-003</t>
+          <t>CP-IMP-036</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Dar de alta una suscripción con el mismo nombre que una suscripción cancelada se acepta</t>
+          <t>El rol anon no puede ejecutar import_transactions</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>US-52, US-58</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -6044,7 +6048,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H146" s="3" t="n"/>
@@ -6052,22 +6056,22 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-004</t>
+          <t>CP-IMP-037</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en UI el alta de suscripción con Nombre vacío o solo espacios</t>
+          <t>Otro usuario no ve transacciones ni imports ajenos</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-77</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -6082,7 +6086,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H147" s="3" t="n"/>
@@ -6090,27 +6094,27 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-005</t>
+          <t>CP-IMP-038</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con Nombre vacío o solo espacios</t>
+          <t>Reintento tras respuesta perdida reconoce lo guardado</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-78</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -6128,7 +6132,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-006</t>
+          <t>CP-IMP-039</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -6138,17 +6142,17 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en UI el alta de suscripción con Nombre igual al de otra activa sin distinguir mayúsculas ni espacios (`" netflix "`)</t>
+          <t>Dos llamadas API con el mismo import_id son idempotentes</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-78</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -6158,7 +6162,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H149" s="3" t="n"/>
@@ -6166,7 +6170,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-007</t>
+          <t>CP-IMP-040</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -6176,12 +6180,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con Nombre igual al de otra activa (`" netflix "`)</t>
+          <t>Sin respuesta conserva Revisión</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-78</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -6204,7 +6208,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-008</t>
+          <t>CP-IMP-041</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -6214,12 +6218,12 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en UI el alta de suscripción con Monto igual a `"0"`</t>
+          <t>Sesión vencida ofrece volver a entrar</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-78</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -6234,7 +6238,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H151" s="3" t="n"/>
@@ -6242,7 +6246,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-009</t>
+          <t>CP-SUS-001</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -6252,7 +6256,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con `p_amount = "0.00"`</t>
+          <t>Dar de alta una suscripción en ARS desde hace 2 meses con día de cobro 10 genera los 2 gastos vencidos al guardar</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -6262,7 +6266,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -6272,7 +6276,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H152" s="3" t="n"/>
@@ -6280,7 +6284,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-010</t>
+          <t>CP-SUS-002</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -6290,17 +6294,17 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` en ARS con Monto mayor al máximo (`"1000000000000.00"`)</t>
+          <t>Dar de alta una suscripción en ARS desde el mes siguiente no genera gastos al guardar</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-52, US-53, US-61</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -6310,7 +6314,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H153" s="3" t="n"/>
@@ -6318,7 +6322,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-011</t>
+          <t>CP-SUS-003</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -6328,12 +6332,12 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con `p_category_id = null`</t>
+          <t>Dar de alta una suscripción con el mismo nombre que una suscripción cancelada se acepta</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>US-52</t>
+          <t>US-52, US-58</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -6348,7 +6352,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H154" s="3" t="n"/>
@@ -6356,7 +6360,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-012</t>
+          <t>CP-SUS-004</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -6366,7 +6370,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con `p_billing_day = 32`</t>
+          <t>Rechazar en UI el alta de suscripción con Nombre vacío o solo espacios</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -6386,7 +6390,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H155" s="3" t="n"/>
@@ -6394,7 +6398,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-013</t>
+          <t>CP-SUS-005</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -6404,7 +6408,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con Mes de inicio anterior al límite inferior (`-25` meses)</t>
+          <t>Rechazar en API `create_subscription` con Nombre vacío o solo espacios</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -6432,17 +6436,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-014</t>
+          <t>CP-SUS-006</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con `p_end_period &lt; p_start_period`</t>
+          <t>Rechazar en UI el alta de suscripción con Nombre igual al de otra activa sin distinguir mayúsculas ni espacios (`" netflix "`)</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -6462,7 +6466,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H157" s="3" t="n"/>
@@ -6470,17 +6474,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-015</t>
+          <t>CP-SUS-007</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con Descripción de 201 caracteres</t>
+          <t>Rechazar en API `create_subscription` con Nombre igual al de otra activa (`" netflix "`)</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -6508,17 +6512,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-016</t>
+          <t>CP-SUS-008</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` con `p_category_id` propia archivada</t>
+          <t>Rechazar en UI el alta de suscripción con Monto igual a `"0"`</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -6538,7 +6542,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H159" s="3" t="n"/>
@@ -6546,7 +6550,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-017</t>
+          <t>CP-SUS-009</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6556,7 +6560,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` usando `p_category_id` de otro usuario</t>
+          <t>Rechazar en API `create_subscription` con `p_amount = "0.00"`</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -6584,17 +6588,17 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-018</t>
+          <t>CP-SUS-010</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API un `INSERT` directo sobre `/rest/v1/subscriptions` con la sesión del usuario</t>
+          <t>Rechazar en API `create_subscription` en ARS con Monto mayor al máximo (`"1000000000000.00"`)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -6622,7 +6626,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-019</t>
+          <t>CP-SUS-011</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -6632,7 +6636,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Dos toques seguidos en `"Guardar suscripción"` deshabilitan el botón y crean una sola suscripción</t>
+          <t>Rechazar en API `create_subscription` con `p_category_id = null`</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -6652,7 +6656,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H162" s="3" t="n"/>
@@ -6660,17 +6664,17 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-020</t>
+          <t>CP-SUS-012</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en UI ver el detalle de una suscripción de otro usuario mostrando `subscription-detail-not-found`</t>
+          <t>Rechazar en API `create_subscription` con `p_billing_day = 32`</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -6698,17 +6702,17 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-021</t>
+          <t>CP-SUS-013</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API leer una suscripción de otro usuario (`GET /rest/v1/subscriptions` devuelve `[]`)</t>
+          <t>Rechazar en API `create_subscription` con Mes de inicio anterior al límite inferior (`-25` meses)</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -6736,17 +6740,17 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-022</t>
+          <t>CP-SUS-014</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `create_subscription` sin sesión autenticada (rol `anon`)</t>
+          <t>Rechazar en API `create_subscription` con `p_end_period &lt; p_start_period`</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -6759,9 +6763,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -6769,16 +6773,12 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>DEF-035</t>
-        </is>
-      </c>
+      <c r="H165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-023</t>
+          <t>CP-SUS-015</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Mostrar estado vacío `subscriptions-empty` y ocultar la tarjeta del total comprometido cuando el usuario no tiene suscripciones</t>
+          <t>Rechazar en API `create_subscription` con Descripción de 201 caracteres</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>US-52, US-63</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H166" s="3" t="n"/>
@@ -6816,27 +6816,27 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-024</t>
+          <t>CP-SUS-016</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Puesta al día automática al entrar a la app genera 2 períodos vencidos pendientes y muestra el aviso `app-catchup-generated`</t>
+          <t>Rechazar en API `create_subscription` con `p_category_id` propia archivada</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>US-53</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H167" s="3" t="n"/>
@@ -6854,7 +6854,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-025</t>
+          <t>CP-SUS-017</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Dos llamadas consecutivas por API a `run_subscription_catchup` responden `200 OK` sin error y dejan exactamente 1 transacción por período</t>
+          <t>Rechazar en API `create_subscription` usando `p_category_id` de otro usuario</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>US-53</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -6892,7 +6892,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-026</t>
+          <t>CP-SUS-018</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Suscripción en estado `paused` no genera ocurrencias al ejecutar `run_subscription_catchup`</t>
+          <t>Rechazar en API un `INSERT` directo sobre `/rest/v1/subscriptions` con la sesión del usuario</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>US-53, US-56</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -6930,22 +6930,22 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-027</t>
+          <t>CP-SUS-019</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Suscripción con día de cobro `31` entre `2026-01` y `2026-04` genera ocurrencias con fechas `31/01/2026`, `28/02/2026`, `31/03/2026` y `30/04/2026`</t>
+          <t>Dos toques seguidos en `"Guardar suscripción"` deshabilitan el botón y crean una sola suscripción</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>US-54, US-55, US-75</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-028</t>
+          <t>CP-SUS-020</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Suscripción con día de cobro `&lt;DIA_MAÑANA&gt;` no genera la ocurrencia del mes corriente</t>
+          <t>Rechazar en UI ver el detalle de una suscripción de otro usuario mostrando `subscription-detail-not-found`</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>US-53, US-55</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H171" s="3" t="n"/>
@@ -7006,7 +7006,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-029</t>
+          <t>CP-SUS-021</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Suscripción con día de cobro igual a `&lt;DIA_HOY&gt;` genera la ocurrencia del mes corriente</t>
+          <t>Rechazar en API leer una suscripción de otro usuario (`GET /rest/v1/subscriptions` devuelve `[]`)</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>US-53, US-55</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H172" s="3" t="n"/>
@@ -7044,7 +7044,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-030</t>
+          <t>CP-SUS-022</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -7054,50 +7054,54 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Pausar suscripción activa con día de cobro `28` (`&gt; &lt;DIA_HOY&gt;`) muestra advertencia de este mes y pasa a `"Pausada desde &lt;HOY&gt;"` con piso en `&lt;MES_SIGUIENTE&gt;`</t>
+          <t>Rechazar en API `create_subscription` sin sesión autenticada (rol `anon`)</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>US-56</t>
+          <t>US-52</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="n"/>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>DEF-035</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-031</t>
+          <t>CP-SUS-023</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>`pause_subscription` por API ejecuta primero la puesta al día y genera los meses vencidos pendientes antes de pausar</t>
+          <t>Mostrar estado vacío `subscriptions-empty` y ocultar la tarjeta del total comprometido cuando el usuario no tiene suscripciones</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>US-56</t>
+          <t>US-52, US-63</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -7112,7 +7116,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H174" s="3" t="n"/>
@@ -7120,7 +7124,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-032</t>
+          <t>CP-SUS-024</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -7130,39 +7134,35 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `pause_subscription` usando la sesión de otro usuario (`404 P0002`)</t>
+          <t>Puesta al día automática al entrar a la app genera 2 períodos vencidos pendientes y muestra el aviso `app-catchup-generated`</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>US-56</t>
+          <t>US-53</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F175" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
-        </is>
-      </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>DEF-034</t>
-        </is>
-      </c>
+          <t>Equipo (informado por mensaje)</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-033</t>
+          <t>CP-SUS-025</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Reanudar suscripción pausada abre `resume-subscription-dialog`, pasa a `"Activa"`, limpia `paused_at`, conserva `generate_from_period = '&lt;MES_SIGUIENTE&gt;-01'` y no genera el mes actual</t>
+          <t>Dos llamadas consecutivas por API a `run_subscription_catchup` responden `200 OK` sin error y dejan exactamente 1 transacción por período</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>US-56, US-57</t>
+          <t>US-53</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H176" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-034</t>
+          <t>CP-SUS-026</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -7210,17 +7210,17 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Cancelar suscripción activa con 4 gastos cargados mantiene el historial en el Detalle y en el Resumen y oculta los botones de acción</t>
+          <t>Suscripción en estado `paused` no genera ocurrencias al ejecutar `run_subscription_catchup`</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>US-58</t>
+          <t>US-53, US-56</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H177" s="3" t="n"/>
@@ -7238,7 +7238,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-035</t>
+          <t>CP-SUS-027</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -7248,17 +7248,17 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Editar el monto de una suscripción activa de `$5.000,00` a `$7.000,00` conserva las 4 ocurrencias ya generadas en `$5.000,00` y muestra Moneda y Mes de inicio como solo lectura</t>
+          <t>Suscripción con día de cobro `31` entre `2026-01` y `2026-04` genera ocurrencias con fechas `31/01/2026`, `28/02/2026`, `31/03/2026` y `30/04/2026`</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>US-59</t>
+          <t>US-54, US-55, US-75</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -7276,22 +7276,22 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-036</t>
+          <t>CP-SUS-028</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API `update_subscription` con `p_end_period` anterior al período corriente (`&lt;MES_ANTERIOR&gt;-01`)</t>
+          <t>Suscripción con día de cobro `&lt;DIA_MAÑANA&gt;` no genera la ocurrencia del mes corriente</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>US-59</t>
+          <t>US-53, US-55</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H179" s="3" t="n"/>
@@ -7314,7 +7314,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-037</t>
+          <t>CP-SUS-029</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en UI renombrar una suscripción poniéndole el nombre de otra suscripción activa del mismo usuario</t>
+          <t>Suscripción con día de cobro igual a `&lt;DIA_HOY&gt;` genera la ocurrencia del mes corriente</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>US-52, US-59</t>
+          <t>US-53, US-55</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -7352,27 +7352,27 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-038</t>
+          <t>CP-SUS-030</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en UI editar una suscripción cancelada al navegar directo a `/subscriptions/&lt;SUB_ID&gt;/edit`</t>
+          <t>Pausar suscripción activa con día de cobro `28` (`&gt; &lt;DIA_HOY&gt;`) muestra advertencia de este mes y pasa a `"Pausada desde &lt;HOY&gt;"` con piso en `&lt;MES_SIGUIENTE&gt;`</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>US-58, US-59</t>
+          <t>US-56</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H181" s="3" t="n"/>
@@ -7390,22 +7390,22 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-039</t>
+          <t>CP-SUS-031</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Rechazar en API cambiar `p_category_id` en `update_subscription` a otra categoría archivada distinta de la actual</t>
+          <t>`pause_subscription` por API ejecuta primero la puesta al día y genera los meses vencidos pendientes antes de pausar</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>US-59</t>
+          <t>US-56</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -7428,7 +7428,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-040</t>
+          <t>CP-SUS-032</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -7438,22 +7438,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Eliminar desde Movimientos la ocurrencia de `&lt;MES_ANTERIOR&gt;` muestra `delete-transaction-subscription-note`, figura con `"Eliminado"` en el Detalle y no vuelve a crearse al recargar</t>
+          <t>Rechazar en API `pause_subscription` usando la sesión de otro usuario (`404 P0002`)</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>US-60</t>
+          <t>US-56</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="F183" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -7461,12 +7461,16 @@
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="H183" s="3" t="n"/>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>DEF-034</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-041</t>
+          <t>CP-SUS-033</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -7476,12 +7480,12 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Mostrar la marca de suscripción en Movimientos y en `"Últimos movimientos"` del Resumen (y no en un gasto manual) y navegar al Detalle al tocarla</t>
+          <t>Reanudar suscripción pausada abre `resume-subscription-dialog`, pasa a `"Activa"`, limpia `paused_at`, conserva `generate_from_period = '&lt;MES_SIGUIENTE&gt;-01'` y no genera el mes actual</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>US-61</t>
+          <t>US-56, US-57</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -7496,7 +7500,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H184" s="3" t="n"/>
@@ -7504,7 +7508,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-042</t>
+          <t>CP-SUS-034</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -7514,17 +7518,17 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>La ocurrencia generada de una suscripción suma en `"Gastado en &lt;mes corto&gt;"` y resta en `"Balance"` del Resumen de V1</t>
+          <t>Cancelar suscripción activa con 4 gastos cargados mantiene el historial en el Detalle y en el Resumen y oculta los botones de acción</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>US-53, US-61</t>
+          <t>US-58</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -7542,7 +7546,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-043</t>
+          <t>CP-SUS-035</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -7552,12 +7556,12 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Suscripción activa en USD con tipo de cambio en `&lt;MES_HACE_2&gt;` y sin tipo de cambio en `&lt;MES_ANTERIOR&gt;` genera solo `&lt;MES_HACE_2&gt;`, muestra `"Falta tipo de cambio"` y el botón `"Cargar tipo de cambio"` navega a `/settings?period=&lt;MES_ANTERIOR&gt;`</t>
+          <t>Editar el monto de una suscripción activa de `$5.000,00` a `$7.000,00` conserva las 4 ocurrencias ya generadas en `$5.000,00` y muestra Moneda y Mes de inicio como solo lectura</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>US-62</t>
+          <t>US-59</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -7572,7 +7576,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Equipo (informado por mensaje)</t>
         </is>
       </c>
       <c r="H186" s="3" t="n"/>
@@ -7580,27 +7584,27 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-044</t>
+          <t>CP-SUS-036</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Con dos suscripciones activas en ARS (`$5.000,00` y `$2.500,00`), el total mensual comprometido muestra `"$7.500,00"` y `"2 suscripciones activas este mes"`</t>
+          <t>Rechazar en API `update_subscription` con `p_end_period` anterior al período corriente (`&lt;MES_ANTERIOR&gt;-01`)</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>US-63</t>
+          <t>US-59</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -7610,7 +7614,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H187" s="3" t="n"/>
@@ -7618,7 +7622,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-045</t>
+          <t>CP-SUS-037</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -7628,12 +7632,12 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Suscripción activa en `USD 10,00` con tipo de cambio del período corriente `1.250,00` suma `"$12.500,00"` al total mensual comprometido</t>
+          <t>Rechazar en UI renombrar una suscripción poniéndole el nombre de otra suscripción activa del mismo usuario</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>US-63</t>
+          <t>US-52, US-59</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -7656,7 +7660,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-046</t>
+          <t>CP-SUS-038</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -7666,12 +7670,12 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Una suscripción en estado `paused` no suma al total mensual comprometido (`"$0,00"` y `"No tenés suscripciones activas este mes"`)</t>
+          <t>Rechazar en UI editar una suscripción cancelada al navegar directo a `/subscriptions/&lt;SUB_ID&gt;/edit`</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>US-63</t>
+          <t>US-58, US-59</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -7686,7 +7690,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>Equipo (informado por mensaje)</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="H189" s="3" t="n"/>
@@ -7694,27 +7698,27 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>CP-SUS-047</t>
+          <t>CP-SUS-039</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Vista previa en `/subscriptions/new` con `$5.000,00` ARS, día `28` (`&gt; &lt;DIA_HOY&gt;`), desde `&lt;MES_HACE_2&gt;` y sin fin muestra 2 meses en `"Se cargan al guardar"`, 3 en `"Próximos cobros"`, resumen de `"$10.000,00"` y al guardar crea exactamente esas 2 transacciones</t>
+          <t>Rechazar en API cambiar `p_category_id` en `update_subscription` a otra categoría archivada distinta de la actual</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>US-52, US-75</t>
+          <t>US-59</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -7732,565 +7736,575 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
+          <t>CP-SUS-040</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Eliminar desde Movimientos la ocurrencia de `&lt;MES_ANTERIOR&gt;` muestra `delete-transaction-subscription-note`, figura con `"Eliminado"` en el Detalle y no vuelve a crearse al recargar</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>US-60</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H191" s="3" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-041</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Mostrar la marca de suscripción en Movimientos y en `"Últimos movimientos"` del Resumen (y no en un gasto manual) y navegar al Detalle al tocarla</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>US-61</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-042</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>La ocurrencia generada de una suscripción suma en `"Gastado en &lt;mes corto&gt;"` y resta en `"Balance"` del Resumen de V1</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>US-53, US-61</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Equipo (informado por mensaje)</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-043</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Suscripción activa en USD con tipo de cambio en `&lt;MES_HACE_2&gt;` y sin tipo de cambio en `&lt;MES_ANTERIOR&gt;` genera solo `&lt;MES_HACE_2&gt;`, muestra `"Falta tipo de cambio"` y el botón `"Cargar tipo de cambio"` navega a `/settings?period=&lt;MES_ANTERIOR&gt;`</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>US-62</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-044</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Con dos suscripciones activas en ARS (`$5.000,00` y `$2.500,00`), el total mensual comprometido muestra `"$7.500,00"` y `"2 suscripciones activas este mes"`</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>US-63</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Equipo (informado por mensaje)</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-045</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Suscripción activa en `USD 10,00` con tipo de cambio del período corriente `1.250,00` suma `"$12.500,00"` al total mensual comprometido</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>US-63</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Equipo (informado por mensaje)</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-046</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Una suscripción en estado `paused` no suma al total mensual comprometido (`"$0,00"` y `"No tenés suscripciones activas este mes"`)</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>US-63</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Equipo (informado por mensaje)</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>CP-SUS-047</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Vista previa en `/subscriptions/new` con `$5.000,00` ARS, día `28` (`&gt; &lt;DIA_HOY&gt;`), desde `&lt;MES_HACE_2&gt;` y sin fin muestra 2 meses en `"Se cargan al guardar"`, 3 en `"Próximos cobros"`, resumen de `"$10.000,00"` y al guardar crea exactamente esas 2 transacciones</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>US-52, US-75</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
           <t>CP-SUS-048</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>Vista previa en `/subscriptions/new` en USD con tipo de cambio en `&lt;MES_HACE_2&gt;` y sin tipo de cambio en `&lt;MES_ANTERIOR&gt;` marca `&lt;MES_ANTERIOR&gt;` con `data-blocked="true"` y no lo cuenta en el resumen</t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>US-75</t>
         </is>
       </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F191" s="8" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>Claude Code</t>
-        </is>
-      </c>
-      <c r="H191" s="3" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
         <is>
           <t>DEF-036</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="9" t="inlineStr">
+    <row r="200"/>
+    <row r="201">
+      <c r="A201" s="9" t="inlineStr">
         <is>
           <t>Resumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="10" t="inlineStr">
-        <is>
-          <t>Planificados</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="10" t="inlineStr">
-        <is>
-          <t>Ejecutados (PASSED + FAILED + DUDA)</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>DUDA (pasa, con dudas)</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="10" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="10" t="inlineStr">
-        <is>
-          <t>No ejecutados</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="10" t="inlineStr">
-        <is>
-          <t>% avance (ejecutados/planificados)</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>98 %</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="10" t="inlineStr">
         <is>
-          <t>% aprobados sobre ejecutados</t>
+          <t>Planificados</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>96 %</t>
+          <t>197</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>Ejecutados con IA (Claude Code)</t>
+          <t>Ejecutados (PASSED + FAILED + DUDA)</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>193</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>Ejecutados a mano por el equipo</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="10" t="inlineStr">
         <is>
-          <t>Informados «ok» por el equipo, sin repetir</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>DUDA (pasa, con dudas)</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="9" t="inlineStr">
-        <is>
-          <t>Por módulo</t>
+      <c r="A207" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
         <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="inlineStr">
+        <is>
+          <t>% avance (ejecutados/planificados)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>98 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
+        <is>
+          <t>% aprobados sobre ejecutados</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>93 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados con IA (Claude Code)</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados a mano por el equipo</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
+        <is>
+          <t>Informados «ok» por el equipo, sin repetir</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="214"/>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>Por módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="inlineStr">
+        <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="B208" s="10" t="inlineStr">
+      <c r="B216" s="10" t="inlineStr">
         <is>
           <t>Casos</t>
         </is>
       </c>
-      <c r="C208" s="10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D208" s="10" t="inlineStr">
+      <c r="C216" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="E208" s="10" t="inlineStr">
+      <c r="E216" s="10" t="inlineStr">
         <is>
           <t>DUDA</t>
         </is>
       </c>
-      <c r="F208" s="10" t="inlineStr">
+      <c r="F216" s="10" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G208" s="10" t="inlineStr">
+      <c r="G216" s="10" t="inlineStr">
         <is>
           <t>No ejecutados</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>DEU-A · Gasto compartido: validaciones de create_transaction (US-34, CP-DEU-005 a 010)</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>DEU-B · Listado, filtro por estado y acceso (US-37 y US-38, CP-DEU-040 a 045)</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>DEU-C · Saldar, volver a pendiente y filtro por dirección (US-39, US-40 y US-79, CP-DEU-046 a 054)</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>DEU-D · Compartir con varias personas (US-82, CP-DEU-055, 056 y 057)</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>DEU-E · Neto de reembolsos en el Resumen (US-30, CP-DEU-058 a 061)</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>DEU-G · Lectura y baja de gastos compartidos, alta de deuda suelta y create_debt por API (US-35, US-36 y US-41; CP-DEU-015 a 035, 16 casos ejecutados con IA)</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>NAV-69 · Barra de navegación (US-69)</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>NAV-70 · Aviso de guardado y reintento (US-70)</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EXP · Exportar CSV (US-47, 31 casos)</t>
+          <t>DEU-H · Gasto compartido con una persona y tope de la deuda (US-34, US-36 y US-41; CP-DEU-001 a 004, 011 a 013 y 025; 8 casos ejecutados con IA)</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -8302,22 +8316,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>IMP · Importar Excel (US-74 a US-79, 41 casos)</t>
+          <t>DEU-A · Gasto compartido: validaciones de create_transaction (US-34, CP-DEU-005 a 010)</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8339,103 +8353,207 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SUS · Suscripciones (US-52 a US-63 y US-75, 48 casos)</t>
+          <t>DEU-B · Listado, filtro por estado y acceso (US-37 y US-38, CP-DEU-040 a 045)</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>DEU-C · Saldar, volver a pendiente y filtro por dirección (US-39, US-40 y US-79, CP-DEU-046 a 054)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>DEU-D · Compartir con varias personas (US-82, CP-DEU-055, 056 y 057)</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="9" t="inlineStr">
-        <is>
-          <t>Por prioridad</t>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>DEU-E · Neto de reembolsos en el Resumen (US-30, CP-DEU-058 a 061)</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="10" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B223" s="10" t="inlineStr">
-        <is>
-          <t>Casos</t>
-        </is>
-      </c>
-      <c r="C223" s="10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D223" s="10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E223" s="10" t="inlineStr">
-        <is>
-          <t>DUDA</t>
-        </is>
-      </c>
-      <c r="F223" s="10" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G223" s="10" t="inlineStr">
-        <is>
-          <t>No ejecutados</t>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>DEU-G · Lectura y baja de gastos compartidos, alta de deuda suelta y create_debt por API (US-35, US-36 y US-41; CP-DEU-015 a 035, 16 casos ejecutados con IA)</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>NAV-69 · Barra de navegación (US-69)</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8445,7 +8563,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8457,22 +8575,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>NAV-70 · Aviso de guardado y reintento (US-70)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8494,188 +8612,423 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>EXP · Exportar CSV (US-47, 31 casos)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>IMP · Importar Excel (US-74 a US-79, 41 casos)</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G227" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="9" t="inlineStr">
-        <is>
-          <t>Defectos abiertos por severidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>Severidad</t>
-        </is>
-      </c>
-      <c r="B230" s="10" t="inlineStr">
-        <is>
-          <t>Abiertos</t>
-        </is>
-      </c>
-      <c r="C230" s="10" t="inlineStr">
-        <is>
-          <t>IDs</t>
-        </is>
-      </c>
-    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SUS · Suscripciones (US-52 a US-63 y US-75, 48 casos)</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="229"/>
+    <row r="230"/>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>Por prioridad</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>Casos</t>
+        </is>
+      </c>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E232" s="10" t="inlineStr">
+        <is>
+          <t>DUDA</t>
+        </is>
+      </c>
+      <c r="F232" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G232" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>4</v>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DEF-030, DEF-031, DEF-032, DEF-037</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>DEF-033, DEF-034, DEF-035, DEF-036</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="9" t="inlineStr">
-        <is>
-          <t>Criterios de salida (docs/07-plan-de-testing.md §6)</t>
-        </is>
-      </c>
-    </row>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="236"/>
+    <row r="237"/>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>1. Cero defectos de severidad Crítica abiertos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Cumplido</t>
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Defectos abiertos por severidad</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2. Cero defectos de severidad Alta abiertos, o justificados por el PO</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Cumplido</t>
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>Severidad</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
+          <t>Abiertos</t>
+        </is>
+      </c>
+      <c r="C239" s="10" t="inlineStr">
+        <is>
+          <t>IDs</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3. Todos los casos de prioridad Alta ejecutados</t>
-        </is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No cumplido: faltan 3 casos de prioridad Alta (BLOCKED por una funcionalidad todavía no implementada: US-82, CP-DEU-055, 056 y 057). Se ejecutan en V3.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4. Toda invariante del alcance con al menos un caso ejecutado</t>
-        </is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>4</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>DEF-030, DEF-031, DEF-032, DEF-037</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>DEF-033, DEF-034, DEF-035, DEF-036</t>
+        </is>
+      </c>
+    </row>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>Criterios de salida (docs/07-plan-de-testing.md §6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1. Cero defectos de severidad Crítica abiertos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Cumplido</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2. Cero defectos de severidad Alta abiertos, o justificados por el PO</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Cumplido</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>3. Todos los casos de prioridad Alta ejecutados</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>No cumplido: 122 de 126 casos de prioridad Alta ejecutados. No ejecutados: 4, todos BLOCKED porque dependen de una funcionalidad todavía no implementada: US-82 (issue #270), CP-DEU-055, 056, 057 y CP-DEU-013. Se ejecutan en V3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>4. Toda invariante del alcance con al menos un caso ejecutado</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
           <t>5. Regresión de V1 ejecutada y defectos corregidos confirmados</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>No evaluado</t>
         </is>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>DUDA</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>DUDA</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>DUDA</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>93 %</t>
+          <t>95 %</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8079,439 +8079,445 @@
         </is>
       </c>
     </row>
-    <row r="200"/>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>CP-CAT-001</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>La torta muestra una porción por categoría, con su monto y su porcentaje</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>US-72</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="n"/>
+    </row>
     <row r="201">
-      <c r="A201" s="9" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>CP-CAT-002</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Los ingresos y los gastos eliminados no entran en la torta</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>US-72</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>CP-CAT-003</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Con 7 categorías, las dos más chicas se agrupan en «Resto» en la torta</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>US-72</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>CP-CAT-004</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Tocar una categoría del Resumen abre su detalle del mes</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>US-73</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>CP-CAT-005</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>En el detalle, «Mes anterior» y «‹ Resumen» conservan la categoría y el mes</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>US-73</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>CP-CAT-006</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Una categoría que no existe muestra un aviso con salida al Resumen</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>US-73</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="n"/>
+    </row>
+    <row r="206"/>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
         <is>
           <t>Resumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="10" t="inlineStr">
-        <is>
-          <t>Planificados</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="10" t="inlineStr">
-        <is>
-          <t>Ejecutados (PASSED + FAILED + DUDA)</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>DUDA (pasa, con dudas)</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="10" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
         <is>
-          <t>No ejecutados</t>
+          <t>Planificados</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>203</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
         <is>
-          <t>% avance (ejecutados/planificados)</t>
+          <t>Ejecutados (PASSED + FAILED + DUDA)</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>98 %</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="10" t="inlineStr">
         <is>
-          <t>% aprobados sobre ejecutados</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>95 %</t>
+          <t>189</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
         <is>
-          <t>Ejecutados con IA (Claude Code)</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
         <is>
-          <t>Ejecutados a mano por el equipo</t>
+          <t>DUDA (pasa, con dudas)</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="10" t="inlineStr">
         <is>
-          <t>Informados «ok» por el equipo, sin repetir</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-    </row>
-    <row r="214"/>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="215">
-      <c r="A215" s="9" t="inlineStr">
-        <is>
-          <t>Por módulo</t>
+      <c r="A215" s="10" t="inlineStr">
+        <is>
+          <t>% avance (ejecutados/planificados)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>98 %</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
         <is>
+          <t>% aprobados sobre ejecutados</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>95 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados con IA (Claude Code)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados a mano por el equipo</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>Informados «ok» por el equipo, sin repetir</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="220"/>
+    <row r="221">
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>Por módulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
+        <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="B216" s="10" t="inlineStr">
+      <c r="B222" s="10" t="inlineStr">
         <is>
           <t>Casos</t>
         </is>
       </c>
-      <c r="C216" s="10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D216" s="10" t="inlineStr">
+      <c r="C222" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D222" s="10" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="E216" s="10" t="inlineStr">
+      <c r="E222" s="10" t="inlineStr">
         <is>
           <t>DUDA</t>
         </is>
       </c>
-      <c r="F216" s="10" t="inlineStr">
+      <c r="F222" s="10" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="G216" s="10" t="inlineStr">
+      <c r="G222" s="10" t="inlineStr">
         <is>
           <t>No ejecutados</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>DEU-H · Gasto compartido con una persona y tope de la deuda (US-34, US-36 y US-41; CP-DEU-001 a 004, 011 a 013 y 025; 8 casos ejecutados con IA)</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>DEU-A · Gasto compartido: validaciones de create_transaction (US-34, CP-DEU-005 a 010)</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>DEU-B · Listado, filtro por estado y acceso (US-37 y US-38, CP-DEU-040 a 045)</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>DEU-C · Saldar, volver a pendiente y filtro por dirección (US-39, US-40 y US-79, CP-DEU-046 a 054)</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>DEU-D · Compartir con varias personas (US-82, CP-DEU-055, 056 y 057)</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>DEU-E · Neto de reembolsos en el Resumen (US-30, CP-DEU-058 a 061)</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>DEU-G · Lectura y baja de gastos compartidos, alta de deuda suelta y create_debt por API (US-35, US-36 y US-41; CP-DEU-015 a 035, 16 casos ejecutados con IA)</t>
+          <t>DEU-H · Gasto compartido con una persona y tope de la deuda (US-34, US-36 y US-41; CP-DEU-001 a 004, 011 a 013 y 025; 8 casos ejecutados con IA)</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -8521,12 +8527,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8538,17 +8544,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>NAV-69 · Barra de navegación (US-69)</t>
+          <t>DEU-A · Gasto compartido: validaciones de create_transaction (US-34, CP-DEU-005 a 010)</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -8575,17 +8581,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NAV-70 · Aviso de guardado y reintento (US-70)</t>
+          <t>DEU-B · Listado, filtro por estado y acceso (US-37 y US-38, CP-DEU-040 a 045)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -8612,22 +8618,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EXP · Exportar CSV (US-47, 31 casos)</t>
+          <t>DEU-C · Saldar, volver a pendiente y filtro por dirección (US-39, US-40 y US-79, CP-DEU-046 a 054)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8649,22 +8655,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>IMP · Importar Excel (US-74 a US-79, 41 casos)</t>
+          <t>DEU-D · Compartir con varias personas (US-82, CP-DEU-055, 056 y 057)</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8674,7 +8680,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -8686,115 +8692,217 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SUS · Suscripciones (US-52 a US-63 y US-75, 48 casos)</t>
+          <t>DEU-E · Neto de reembolsos en el Resumen (US-30, CP-DEU-058 a 061)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DEU-G · Lectura y baja de gastos compartidos, alta de deuda suelta y create_debt por API (US-35, US-36 y US-41; CP-DEU-015 a 035, 16 casos ejecutados con IA)</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NAV-69 · Barra de navegación (US-69)</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>NAV-70 · Aviso de guardado y reintento (US-70)</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>EXP · Exportar CSV (US-47, 31 casos)</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231">
-      <c r="A231" s="9" t="inlineStr">
-        <is>
-          <t>Por prioridad</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="10" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="B232" s="10" t="inlineStr">
-        <is>
-          <t>Casos</t>
-        </is>
-      </c>
-      <c r="C232" s="10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="D232" s="10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E232" s="10" t="inlineStr">
-        <is>
-          <t>DUDA</t>
-        </is>
-      </c>
-      <c r="F232" s="10" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="G232" s="10" t="inlineStr">
-        <is>
-          <t>No ejecutados</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>IMP · Importar Excel (US-74 a US-79, 41 casos)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -8806,22 +8914,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>SUS · Suscripciones (US-52 a US-63 y US-75, 48 casos)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -8843,22 +8951,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>CAT · Resumen por categoría (US-72 y US-73, 6 casos)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -8882,153 +8990,310 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>Defectos abiertos por severidad</t>
+          <t>Por prioridad</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="10" t="inlineStr">
         <is>
-          <t>Severidad</t>
+          <t>Prioridad</t>
         </is>
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>Abiertos</t>
+          <t>Casos</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>IDs</t>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E239" s="10" t="inlineStr">
+        <is>
+          <t>DUDA</t>
+        </is>
+      </c>
+      <c r="F239" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G239" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>0</v>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>0</v>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>4</v>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DEF-030, DEF-031, DEF-032, DEF-037</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>DEF-033, DEF-034, DEF-035, DEF-036</t>
-        </is>
-      </c>
-    </row>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="243"/>
     <row r="244"/>
-    <row r="245"/>
+    <row r="245">
+      <c r="A245" s="9" t="inlineStr">
+        <is>
+          <t>Defectos abiertos por severidad</t>
+        </is>
+      </c>
+    </row>
     <row r="246">
-      <c r="A246" s="9" t="inlineStr">
-        <is>
-          <t>Criterios de salida (docs/07-plan-de-testing.md §6)</t>
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>Severidad</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>Abiertos</t>
+        </is>
+      </c>
+      <c r="C246" s="10" t="inlineStr">
+        <is>
+          <t>IDs</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1. Cero defectos de severidad Crítica abiertos</t>
-        </is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Cumplido</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2. Cero defectos de severidad Alta abiertos, o justificados por el PO</t>
-        </is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Cumplido</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3. Todos los casos de prioridad Alta ejecutados</t>
-        </is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>4</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No cumplido: 122 de 126 casos de prioridad Alta ejecutados. No ejecutados: 4, todos BLOCKED porque dependen de una funcionalidad todavía no implementada: US-82 (issue #270), CP-DEU-055, 056, 057 y CP-DEU-013. Se ejecutan en V3.</t>
+          <t>DEF-030, DEF-031, DEF-032, DEF-037</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>DEF-033, DEF-034, DEF-035, DEF-036</t>
+        </is>
+      </c>
+    </row>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>Criterios de salida (docs/07-plan-de-testing.md §6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1. Cero defectos de severidad Crítica abiertos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Cumplido</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2. Cero defectos de severidad Alta abiertos, o justificados por el PO</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Cumplido</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>3. Todos los casos de prioridad Alta ejecutados</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>No cumplido: 125 de 129 casos de prioridad Alta ejecutados. No ejecutados: 4, todos BLOCKED porque dependen de una funcionalidad todavía no implementada: US-82 (issue #270), CP-DEU-055, 056, 057 y CP-DEU-013. Se ejecutan en V3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
           <t>4. Toda invariante del alcance con al menos un caso ejecutado</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>5. Regresión de V1 ejecutada y defectos corregidos confirmados</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>No evaluado</t>
         </is>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -9295,7 +9295,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Parcial: confirmación de defectos de V1 ejecutada el 2026-10-28: 21 de 22 confirmados corregidos en V2 y 1 no concluyente (DEF-023). La regresión de los casos de V1 seleccionados (03) todavía no se ejecutó.</t>
         </is>
       </c>
     </row>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -9295,7 +9295,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Parcial: confirmación de defectos de V1 ejecutada el 2026-10-28: 21 de 22 confirmados corregidos en V2 y 1 no concluyente (DEF-023). La regresión de los casos de V1 seleccionados (03) todavía no se ejecutó.</t>
+          <t>Parcial: confirmación de defectos de V1 ejecutada el 2026-10-28: 21 de 22 confirmados corregidos en V2 y 1 no concluyente (DEF-023, cerrado igual por decisión del equipo). La regresión de los casos de V1 seleccionados (03) todavía no se ejecutó.</t>
         </is>
       </c>
     </row>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biyu - entrega 2 - Reporte de ejecución de test cases · Deudas, Navegación, Exportar CSV, Importar Excel y Suscripciones</t>
+          <t>Biyu - entrega 2 - Reporte de ejecución de test cases · Deudas, Navegación, Exportar CSV, Importar Excel, Suscripciones y Resumen por categoría, y regresión de V1</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No cumplido: 125 de 129 casos de prioridad Alta ejecutados. No ejecutados: 4, todos BLOCKED porque dependen de una funcionalidad todavía no implementada: US-82 (issue #270), CP-DEU-055, 056, 057 y CP-DEU-013. Se ejecutan en V3.</t>
+          <t>No cumplido: 125 de 129 casos de prioridad Alta ejecutados. No ejecutados: 4, todos BLOCKED porque dependen de una funcionalidad todavía no implementada: US-82 (issue #270), CP-DEU-055, 056, 057 y CP-DEU-013. Se ejecutan en V3. En la regresión de V1 se ejecutaron los 39 casos de prioridad Alta (39 PASSED, con IA).</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Parcial: Deudas y Navegación: I10, I18, I2, I3, I4, I5, I7 e I9 con casos ejecutados. I1 e I1' se ejecutaron en la regresión de V1 (CP-CUO-004, 005, 010 y 013, y CP-REG-015: PASSED). En Exportar, Importar y Suscripciones no se verificó invariante por invariante en este reporte. Las demás invariantes de V2 (dashboard, etc.) están en otros casos.</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,2707 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Parcial: confirmación de defectos de V1 ejecutada el 2026-10-28: 21 de 22 confirmados corregidos en V2 y 1 no concluyente (DEF-023, cerrado igual por decisión del equipo). La regresión de los casos de V1 seleccionados (03) todavía no se ejecutó.</t>
+          <t>Cumplido, con salvedades: Confirmación de defectos de V1 ejecutada el 2026-10-28: 18 confirmados corregidos en V2, 3 confirmados en parte (DEF-021, DEF-027 y DEF-028) y 1 no concluyente (DEF-023, de severidad Alta, cerrado por decisión del equipo; se reabre si reaparece). Regresión de los 60 casos de V1 seleccionados (`03`) ejecutada el 2026-10-28 con IA: 60 PASSED, sin defectos nuevos. Salvedades: todo se verificó en local (DEF-005 depende de la configuración de Auth del proyecto hosteado, que no se verificó) y el repaso manual de los 39 casos de prioridad Alta está pendiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>Regresión de V1 sobre V2 (60 casos de 03-seleccion-regresion, 2026-10-28; no suma a los casos de arriba)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Test case ID</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>User story</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Camino feliz</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Ejecutó</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>Defectos</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-001</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Sin sesión, la app redirige al login</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-002</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Una ruta privada abierta sin sesión conserva el destino</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-003</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Crear una cuenta con email y contraseña válidos</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>US-50, US-51</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-004</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Contraseñas que no cumplen los criterios se rechazan</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>US-50, US-67</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-005</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>No se puede crear una cuenta con un email ya registrado</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>US-50</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-008</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Una cuenta nueva tiene el catálogo inicial sembrado</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>US-43, US-51</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-009</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Cerrar sesión y no poder volver con "atrás"</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>US-64</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-011</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento entre usuarios en todas las tablas (par de autorización)</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>CP-ACC-012</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Contraseña y confirmación distintas bloquean el alta</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>US-66</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-001</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Crear una categoría con nombre y color</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>US-42</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-003</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>No se permiten dos categorías activas con el mismo nombre</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>US-42</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-004</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Archivar una categoría con historia</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>US-44</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-005</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Reusar el nombre de una categoría archivada</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>US-42, US-44</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-006</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Crear una cuenta de tarjeta de crédito</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>US-45</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-007</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>No se permiten dos cuentas activas con el mismo nombre</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>US-45</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-008</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>La siembra concurrente no duplica el catálogo</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>US-43</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-009</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Cargar y actualizar el tipo de cambio de referencia del mes</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>US-46</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-010</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de cambio de referencia en cero o negativo</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>US-46</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-011</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Después de crear la cuenta aparece la configuración inicial</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>US-68</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>CP-CFG-013</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Destildar una categoría en el setup la archiva</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>US-68</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-001</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>El registro es la pantalla de inicio</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>US-01</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-002</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>La fecha viene precargada con hoy</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>US-03</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-004</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Elegir la categoría tocando un chip</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>US-06</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-005</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Una categoría archivada no se ofrece ni se acepta por API</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>US-06</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-008</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Fecha de ayer sí, fecha de mañana no</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-009</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Confirmación y formulario limpio después de guardar</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>US-10</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-010</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Monto vacío, cero o negativo no se guarda</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>US-11</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-011</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Monto con tres decimales</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>US-11</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-012</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Eliminar una transacción la saca del total del mes</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>US-65</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-013</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Eliminar una compra con cuotas en meses cerrados avisa y es retroactivo</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>US-65, US-18</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-014</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Otro usuario no puede leer ni borrar una transacción ajena</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-015</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>No se puede escribir en transactions salteando la RPC</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>US-11</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>CP-REG-016</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>El monto toma el foco con teclado numérico</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>US-02</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-001</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>Compra en 12 cuotas genera 12 imputaciones consecutivas</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>US-12</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-002</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Previsualización del impacto mensual antes de guardar</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>US-13</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-003</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>Cambiar a una cuenta que no es crédito resetea las cuotas</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>US-14</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-004</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>División exacta: 12 cuotas iguales</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>US-15</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-005</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>El resto lo absorbe la última cuota</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>US-15</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-006</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Cantidad de cuotas: 0, 1, 2, 12 y 13</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>US-15, US-12</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-007</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>El Resumen separa las cuotas de meses anteriores</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>US-16</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-009</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>Borrar una compra en cuotas saca todas sus cuotas</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>US-18</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-010</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>En USD, la suma en pesos de las cuotas es exacta</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>US-15</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-011</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Otro usuario no ve las cuotas de una compra ajena</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-012</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Un ingreso no admite cuotas aunque la cuenta sea crédito</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>US-12, US-14</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>CP-CUO-013</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>Un fallo a mitad de create_transaction no deja datos parciales</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>US-15</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>CP-MON-001</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Gasto en USD con el tipo de cambio sugerido</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>US-19</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>CP-MON-002</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Tabla de decisión de moneda y tipo de cambio (6 filas)</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>US-19</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>CP-MON-003</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>Pisar el tipo de cambio sugerido</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>US-20, US-21</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>CP-MON-004</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>Cambiar la referencia no altera lo ya guardado</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>US-22</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>CP-MON-005</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>El total del mes en pesos incluye lo gastado en dólares</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>US-23</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>CP-MON-007</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Otro usuario no lee ni modifica el tipo de cambio ajeno</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-001</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>El Resumen abre en el mes actual con su total</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>US-25</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-002</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>El mes elegido vive en la URL</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>US-26</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-003</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>Período inválido o ausente cae al mes actual</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>US-26</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-004</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>Gasto por categoría en barras</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>US-27</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-005</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>Gasto por cuenta</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>US-28</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-006</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Ingresos y balance positivo</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>US-29</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-008</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>Últimos 10 movimientos con acceso a la lista completa</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>US-31</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-010</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>Mes sin datos: estado vacío con acceso al registro</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>US-33</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H321" s="3" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>CP-DAS-011</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>El Resumen de un usuario nunca muestra datos de otro</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>US-48</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="inlineStr">
+        <is>
+          <t>Resumen de la regresión</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="10" t="inlineStr">
+        <is>
+          <t>Planificados</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="10" t="inlineStr">
+        <is>
+          <t>% avance (ejecutados/planificados)</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="10" t="inlineStr">
+        <is>
+          <t>% aprobados sobre ejecutados</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="10" t="inlineStr">
+        <is>
+          <t>Ejecutados con IA (Claude Code)</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="10" t="inlineStr">
+        <is>
+          <t>Repasados a mano por el equipo (prioridad Alta)</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>pendiente (0 de 39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="10" t="inlineStr">
+        <is>
+          <t>Cambiaron de estado respecto de E1</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>CP-ACC-004 y CP-CFG-004: FAILED → PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="9" t="inlineStr">
+        <is>
+          <t>Por módulo de V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="10" t="inlineStr">
+        <is>
+          <t>Módulo</t>
+        </is>
+      </c>
+      <c r="B338" s="10" t="inlineStr">
+        <is>
+          <t>Casos</t>
+        </is>
+      </c>
+      <c r="C338" s="10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D338" s="10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E338" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F338" s="10" t="inlineStr">
+        <is>
+          <t>No ejecutados</t>
+        </is>
+      </c>
+      <c r="G338" s="10" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ACC · Acceso</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>CFG · Configuración</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>REG · Registro</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>CUO · Cuotas</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>MON · Monedas</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>DAS · Resumen</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -8877,7 +8877,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>IMP · Importar Excel (US-74 a US-79, 41 casos)</t>
+          <t>IMP · Importar Excel (US-74, US-76, US-77 y US-78, 41 casos)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -9299,6 +9299,8 @@
         </is>
       </c>
     </row>
+    <row r="259"/>
+    <row r="260"/>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
@@ -11628,6 +11630,7 @@
       </c>
       <c r="H322" s="3" t="n"/>
     </row>
+    <row r="323"/>
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
@@ -11767,6 +11770,7 @@
         </is>
       </c>
     </row>
+    <row r="336"/>
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H7" s="3" t="n"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H8" s="3" t="n"/>
@@ -818,7 +818,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H9" s="3" t="n"/>
@@ -856,7 +856,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H10" s="3" t="n"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H11" s="3" t="n"/>
@@ -932,7 +932,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H12" s="3" t="n"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H55" s="3" t="n"/>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H56" s="3" t="n"/>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H57" s="3" t="n"/>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H58" s="3" t="n"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H62" s="3" t="n"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H63" s="3" t="n"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H64" s="3" t="n"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H65" s="3" t="n"/>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H66" s="3" t="n"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H67" s="3" t="n"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H73" s="3" t="n"/>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H75" s="3" t="n"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H77" s="3" t="n"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H78" s="3" t="n"/>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>A mano</t>
         </is>
       </c>
       <c r="H79" s="3" t="n"/>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -8307,7 +8307,6 @@
       </c>
       <c r="H205" s="3" t="n"/>
     </row>
-    <row r="206"/>
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
@@ -8459,7 +8458,6 @@
         </is>
       </c>
     </row>
-    <row r="220"/>
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
@@ -8985,8 +8983,6 @@
         </is>
       </c>
     </row>
-    <row r="236"/>
-    <row r="237"/>
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
@@ -9142,8 +9138,6 @@
         </is>
       </c>
     </row>
-    <row r="243"/>
-    <row r="244"/>
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
@@ -9230,8 +9224,6 @@
         </is>
       </c>
     </row>
-    <row r="251"/>
-    <row r="252"/>
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
@@ -9295,12 +9287,10 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Cumplido, con salvedades: Confirmación de defectos de V1 ejecutada el 2026-10-28: 18 confirmados corregidos en V2, 3 confirmados en parte (DEF-021, DEF-027 y DEF-028) y 1 no concluyente (DEF-023, de severidad Alta, cerrado por decisión del equipo; se reabre si reaparece). Regresión de los 60 casos de V1 seleccionados (`03`) ejecutada el 2026-10-28 con IA: 60 PASSED, sin defectos nuevos. Salvedades: todo se verificó en local (DEF-005 depende de la configuración de Auth del proyecto hosteado, que no se verificó) y el repaso manual de los 39 casos de prioridad Alta está pendiente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="259"/>
-    <row r="260"/>
+          <t>Cumplido, con salvedades: Confirmación de defectos de V1 ejecutada el 2026-10-28: 18 confirmados corregidos en V2, 3 confirmados en parte (DEF-021, DEF-027 y DEF-028) y 1 no concluyente (DEF-023, de severidad Alta, cerrado por decisión del equipo; se reabre si reaparece). Regresión de los 60 casos de V1 seleccionados (`03`) ejecutada el 2026-10-28 con IA: 60 PASSED, sin defectos nuevos. Salvedades: todo se verificó en local (DEF-005 depende de la configuración de Auth del proyecto hosteado, que no se verificó) y el repaso manual del equipo no dejó capturas ni un resultado por caso.</t>
+        </is>
+      </c>
+    </row>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
@@ -11630,7 +11620,6 @@
       </c>
       <c r="H322" s="3" t="n"/>
     </row>
-    <row r="323"/>
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
@@ -11749,12 +11738,12 @@
     <row r="334">
       <c r="A334" s="10" t="inlineStr">
         <is>
-          <t>Repasados a mano por el equipo (prioridad Alta)</t>
+          <t>Repasados a mano por el equipo</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>pendiente (0 de 39)</t>
+          <t>60 de 60</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11759,6 @@
         </is>
       </c>
     </row>
-    <row r="336"/>
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -8458,6 +8458,18 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>Repaso manual posterior (después de Claude Code)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>DEU: Mariana · NAV: Santiago · EXP: Joaquín · IMP: Valentina · SUS: Micaela · CAT y regresión de V1: el equipo</t>
+        </is>
+      </c>
+    </row>
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>

--- a/entrega-2/06-reporte-de-ejecucion.xlsx
+++ b/entrega-2/06-reporte-de-ejecucion.xlsx
@@ -8461,12 +8461,12 @@
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
         <is>
-          <t>Repaso manual posterior (después de Claude Code)</t>
+          <t>Repaso manual posterior en el deploy (después de Claude Code)</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DEU: Mariana · NAV: Santiago · EXP: Joaquín · IMP: Valentina · SUS: Micaela · CAT y regresión de V1: el equipo</t>
+          <t>DEU: Mariana · NAV: Santiago · EXP: Joaquín · IMP: Valentina · SUS: Micaela · CAT: el equipo · Regresión de V1: Joaquín</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Cumplido, con salvedades: Confirmación de defectos de V1 ejecutada el 2026-10-28: 18 confirmados corregidos en V2, 3 confirmados en parte (DEF-021, DEF-027 y DEF-028) y 1 no concluyente (DEF-023, de severidad Alta, cerrado por decisión del equipo; se reabre si reaparece). Regresión de los 60 casos de V1 seleccionados (`03`) ejecutada el 2026-10-28 con IA: 60 PASSED, sin defectos nuevos. Salvedades: todo se verificó en local (DEF-005 depende de la configuración de Auth del proyecto hosteado, que no se verificó) y el repaso manual del equipo no dejó capturas ni un resultado por caso.</t>
+          <t>Cumplido, con salvedades: Confirmación de defectos de V1 ejecutada el 2026-10-28: 18 confirmados corregidos en V2, 3 confirmados en parte (DEF-021, DEF-027 y DEF-028) y 1 no concluyente (DEF-023, de severidad Alta, cerrado por decisión del equipo; se reabre si reaparece). Regresión de los 60 casos de V1 seleccionados (`03`) ejecutada el 2026-10-28 con IA: 60 PASSED, sin defectos nuevos. Salvedades: todo se verificó en local (DEF-005 depende de la configuración de Auth del proyecto hosteado, que no se verificó) y el repaso manual posterior se hizo en el deploy.</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
     <row r="334">
       <c r="A334" s="10" t="inlineStr">
         <is>
-          <t>Repasados a mano por el equipo</t>
+          <t>Ejecutados a mano por Joaquín en el deploy</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
